--- a/報告資料/月報2026年度_渡辺晃佑.xlsx
+++ b/報告資料/月報2026年度_渡辺晃佑.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10717"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="121" documentId="11_49F784EBFFCED6F7B43269BFA3399221FDFFDBD5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDB6E5E0-C282-0B4A-8D04-6357EE83EE0F}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabe\Desktop\claude\月次報告\報告資料\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4408AA-6D55-46DE-9A91-ED54FF0F64B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="7" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="書き方" sheetId="1" r:id="rId1"/>
@@ -20,37 +25,36 @@
     <sheet name="5月度" sheetId="10" r:id="rId10"/>
     <sheet name="6月度" sheetId="11" r:id="rId11"/>
     <sheet name="7月度" sheetId="12" r:id="rId12"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId13"/>
-    <sheet name="8月度" sheetId="13" r:id="rId14"/>
-    <sheet name="9月度" sheetId="14" r:id="rId15"/>
-    <sheet name="10月度" sheetId="15" r:id="rId16"/>
-    <sheet name="11月度" sheetId="16" r:id="rId17"/>
-    <sheet name="12月度" sheetId="17" r:id="rId18"/>
-    <sheet name="Sheet9" sheetId="18" r:id="rId19"/>
+    <sheet name="8月度" sheetId="13" r:id="rId13"/>
+    <sheet name="9月度" sheetId="14" r:id="rId14"/>
+    <sheet name="10月度" sheetId="15" r:id="rId15"/>
+    <sheet name="11月度" sheetId="16" r:id="rId16"/>
+    <sheet name="12月度" sheetId="17" r:id="rId17"/>
+    <sheet name="Sheet9" sheetId="18" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'様式 '!$A$1:$A$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'9月度（サンプル）'!$A$1:$A$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14">'10月度'!$A$1:$A$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15">'11月度'!$A$1:$A$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">'11月度（2025年度）'!$A$1:$A$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16">'12月度'!$A$1:$A$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'12月度(2025)'!$A$1:$A$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">'5月度'!$A$1:$A$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10">'6月度'!$A$1:$A$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">'7月度'!$A$1:$A$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13">'8月度'!$A$1:$A$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14">'9月度'!$A$1:$A$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15">'10月度'!$A$1:$A$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16">'11月度'!$A$1:$A$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17">'12月度'!$A$1:$A$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'10月度'!$A$1:$F$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'11月度'!$A$1:$F$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12">'8月度'!$A$1:$A$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13">'9月度'!$A$1:$A$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'9月度（サンプル）'!$A$1:$A$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'様式 '!$A$1:$A$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'10月度'!$A$1:$F$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'11月度'!$A$1:$F$50</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'11月度（2025年度）'!$A$1:$F$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="17">'12月度'!$A$1:$F$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'12月度'!$A$1:$F$50</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'12月度(2025)'!$A$1:$F$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'5月度'!$A$1:$F$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'6月度'!$A$1:$F$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'7月度'!$A$1:$F$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'8月度'!$A$1:$F$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'9月度'!$A$1:$F$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'8月度'!$A$1:$F$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'9月度'!$A$1:$F$50</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'9月度（サンプル）'!$A$1:$I$80</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'様式 '!$A$1:$F$50</definedName>
   </definedNames>
@@ -78,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="292">
   <si>
     <t>サンプルを元に各自記入すること。</t>
   </si>
@@ -1108,7 +1112,7 @@
     <numFmt numFmtId="176" formatCode="[$-411]yyyy/mm/dd"/>
     <numFmt numFmtId="177" formatCode="[$-411]mm&quot;月&quot;dd&quot;日&quot;"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1337,6 +1341,12 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -1803,7 +1813,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2125,9 +2135,6 @@
     <xf numFmtId="56" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2143,13 +2150,13 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4967,33 +4974,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:B5"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="3.6796875" customWidth="1"/>
-    <col min="2" max="1025" width="8.7265625" customWidth="1"/>
+    <col min="1" max="1" width="3.625" customWidth="1"/>
+    <col min="2" max="1025" width="8.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:2">
       <c r="B3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:2">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.1">
+    <row r="5" spans="2:2">
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="33"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -5002,18 +5010,18 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B1:F48"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="23.86328125" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="23.875" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:5">
       <c r="B1" s="1" t="s">
         <v>217</v>
       </c>
@@ -5021,7 +5029,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
         <v>89</v>
       </c>
@@ -5035,7 +5043,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:5">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -5049,7 +5057,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:5">
       <c r="B4" s="74" t="s">
         <v>134</v>
       </c>
@@ -5063,11 +5071,11 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:5">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -5075,11 +5083,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B6" s="120" t="s">
+    <row r="6" spans="2:5" ht="13.9" customHeight="1">
+      <c r="B6" s="119" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="120"/>
+      <c r="C6" s="119"/>
       <c r="D6" s="76" t="s">
         <v>139</v>
       </c>
@@ -5087,7 +5095,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:5">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -5101,7 +5109,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>141</v>
       </c>
@@ -5115,27 +5123,27 @@
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:5" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-    </row>
-    <row r="10" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+    </row>
+    <row r="10" spans="2:5" ht="13.5" customHeight="1">
       <c r="B10" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="C10" s="121" t="s">
+      <c r="C10" s="120" t="s">
         <v>144</v>
       </c>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.1">
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" s="82" t="s">
         <v>24</v>
       </c>
@@ -5143,29 +5151,29 @@
       <c r="D11" s="84"/>
       <c r="E11" s="85"/>
     </row>
-    <row r="12" spans="2:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B12" s="125" t="s">
+    <row r="12" spans="2:5" ht="13.9" customHeight="1">
+      <c r="B12" s="124" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-    </row>
-    <row r="13" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B13" s="123" t="s">
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+    </row>
+    <row r="13" spans="2:5" ht="16.5" customHeight="1">
+      <c r="B13" s="122" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
-    </row>
-    <row r="14" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B14" s="124"/>
-      <c r="C14" s="124"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124"/>
-    </row>
-    <row r="15" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+    </row>
+    <row r="14" spans="2:5" ht="16.5" customHeight="1">
+      <c r="B14" s="123"/>
+      <c r="C14" s="123"/>
+      <c r="D14" s="123"/>
+      <c r="E14" s="123"/>
+    </row>
+    <row r="15" spans="2:5" ht="16.5" customHeight="1">
       <c r="B15" s="25" t="s">
         <v>26</v>
       </c>
@@ -5173,7 +5181,7 @@
       <c r="D15" s="23"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="16" spans="2:5" ht="16.5" customHeight="1">
       <c r="B16" s="25" t="s">
         <v>27</v>
       </c>
@@ -5181,13 +5189,13 @@
       <c r="D16" s="23"/>
       <c r="E16" s="27"/>
     </row>
-    <row r="17" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="17" spans="2:6" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="27"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:6">
       <c r="B18" s="29" t="s">
         <v>28</v>
       </c>
@@ -5197,7 +5205,7 @@
       <c r="D18" s="94"/>
       <c r="F18" s="95"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:6">
       <c r="B19" s="29"/>
       <c r="C19" s="90" t="s">
         <v>181</v>
@@ -5207,7 +5215,7 @@
       </c>
       <c r="F19" s="96"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:6">
       <c r="B20" s="29"/>
       <c r="C20" s="88" t="s">
         <v>165</v>
@@ -5220,7 +5228,7 @@
       </c>
       <c r="F20" s="97"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:6">
       <c r="B21" s="29"/>
       <c r="C21" s="88" t="s">
         <v>167</v>
@@ -5230,7 +5238,7 @@
       </c>
       <c r="F21" s="97"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:6">
       <c r="B22" s="29"/>
       <c r="C22" s="88" t="s">
         <v>200</v>
@@ -5243,7 +5251,7 @@
       </c>
       <c r="F22" s="97"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:6">
       <c r="B23" s="29"/>
       <c r="C23" s="90" t="s">
         <v>202</v>
@@ -5253,7 +5261,7 @@
       </c>
       <c r="F23" s="97"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:6">
       <c r="B24" s="29"/>
       <c r="C24" s="90" t="s">
         <v>204</v>
@@ -5263,18 +5271,18 @@
       </c>
       <c r="F24" s="97"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:6">
       <c r="B25" s="29"/>
       <c r="F25" s="97"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:6">
       <c r="B26" s="29"/>
       <c r="C26" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F26" s="97"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:6">
       <c r="B27" s="29"/>
       <c r="C27" s="81" t="s">
         <v>165</v>
@@ -5284,7 +5292,7 @@
       </c>
       <c r="F27" s="97"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:6">
       <c r="B28" s="29"/>
       <c r="C28" s="81" t="s">
         <v>167</v>
@@ -5294,7 +5302,7 @@
       </c>
       <c r="E28" s="30"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:6">
       <c r="B29" s="29"/>
       <c r="C29" t="s">
         <v>202</v>
@@ -5304,15 +5312,15 @@
       </c>
       <c r="E29" s="30"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:6">
       <c r="B30" s="29"/>
       <c r="E30" s="30"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:6">
       <c r="B31" s="31"/>
       <c r="E31" s="30"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:6">
       <c r="B32" s="29" t="s">
         <v>29</v>
       </c>
@@ -5321,11 +5329,11 @@
       </c>
       <c r="E32" s="30"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:5">
       <c r="B33" s="31"/>
       <c r="E33" s="30"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:5">
       <c r="B34" s="29" t="s">
         <v>30</v>
       </c>
@@ -5334,14 +5342,14 @@
       </c>
       <c r="E34" s="30"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:5">
       <c r="B35" s="31"/>
       <c r="C35" t="s">
         <v>231</v>
       </c>
       <c r="E35" s="30"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:5">
       <c r="B36" s="29" t="s">
         <v>31</v>
       </c>
@@ -5350,11 +5358,11 @@
       </c>
       <c r="E36" s="30"/>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:5">
       <c r="B37" s="31"/>
       <c r="E37" s="30"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:5">
       <c r="B38" s="29" t="s">
         <v>32</v>
       </c>
@@ -5363,15 +5371,15 @@
       </c>
       <c r="E38" s="30"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:5">
       <c r="B39" s="29"/>
       <c r="E39" s="30"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:5">
       <c r="B40" s="29"/>
       <c r="E40" s="30"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="41" spans="2:5">
       <c r="B41" s="32" t="s">
         <v>33</v>
       </c>
@@ -5380,47 +5388,47 @@
       </c>
       <c r="E41" s="30"/>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:5">
       <c r="B42" s="34"/>
       <c r="C42" s="1" t="s">
         <v>234</v>
       </c>
       <c r="E42" s="30"/>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:5">
       <c r="B43" s="34"/>
       <c r="C43" s="33" t="s">
         <v>35</v>
       </c>
       <c r="E43" s="30"/>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:5">
       <c r="B44" s="34"/>
       <c r="C44" s="33" t="s">
         <v>235</v>
       </c>
       <c r="E44" s="30"/>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="45" spans="2:5">
       <c r="B45" s="34"/>
       <c r="C45" s="33"/>
       <c r="E45" s="30"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:5">
       <c r="B46" s="31"/>
       <c r="C46" s="33" t="s">
         <v>36</v>
       </c>
       <c r="E46" s="30"/>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:5">
       <c r="B47" s="34"/>
       <c r="C47" s="33" t="s">
         <v>190</v>
       </c>
       <c r="E47" s="30"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:5">
       <c r="B48" s="36"/>
       <c r="C48" s="37"/>
       <c r="D48" s="38"/>
@@ -5436,6 +5444,7 @@
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0900-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -5454,18 +5463,18 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="B1:E53"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="20.31640625" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:5">
       <c r="B1" s="1" t="s">
         <v>253</v>
       </c>
@@ -5473,7 +5482,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2" spans="2:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:5" ht="14.25" thickBot="1">
       <c r="B2" s="1" t="s">
         <v>89</v>
       </c>
@@ -5487,7 +5496,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="14.25" thickTop="1" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:5" ht="14.25" thickTop="1">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -5501,7 +5510,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:5">
       <c r="B4" s="74" t="s">
         <v>134</v>
       </c>
@@ -5515,11 +5524,11 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:5">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -5527,11 +5536,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B6" s="120" t="s">
+    <row r="6" spans="2:5">
+      <c r="B6" s="119" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="120"/>
+      <c r="C6" s="119"/>
       <c r="D6" s="76" t="s">
         <v>139</v>
       </c>
@@ -5539,7 +5548,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:5">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -5553,7 +5562,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>141</v>
       </c>
@@ -5567,23 +5576,23 @@
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:5" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-    </row>
-    <row r="10" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+    </row>
+    <row r="10" spans="2:5" ht="13.5" customHeight="1">
       <c r="B10" s="17"/>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
-    </row>
-    <row r="11" spans="2:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.15">
+      <c r="C10" s="114"/>
+      <c r="D10" s="114"/>
+      <c r="E10" s="114"/>
+    </row>
+    <row r="11" spans="2:5" ht="14.25" thickBot="1">
       <c r="B11" s="18" t="s">
         <v>24</v>
       </c>
@@ -5591,29 +5600,29 @@
       <c r="D11" s="20"/>
       <c r="E11" s="21"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B12" s="125" t="s">
+    <row r="12" spans="2:5">
+      <c r="B12" s="124" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B13" s="123" t="s">
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="B13" s="122" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
-    </row>
-    <row r="14" spans="2:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="124"/>
-      <c r="C14" s="124"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124"/>
-    </row>
-    <row r="15" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+    </row>
+    <row r="14" spans="2:5" ht="16.5" customHeight="1" thickBot="1">
+      <c r="B14" s="123"/>
+      <c r="C14" s="123"/>
+      <c r="D14" s="123"/>
+      <c r="E14" s="123"/>
+    </row>
+    <row r="15" spans="2:5" ht="16.5" customHeight="1">
       <c r="B15" s="25" t="s">
         <v>26</v>
       </c>
@@ -5621,7 +5630,7 @@
       <c r="D15" s="23"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="16" spans="2:5" ht="16.5" customHeight="1">
       <c r="B16" s="25" t="s">
         <v>27</v>
       </c>
@@ -5629,13 +5638,13 @@
       <c r="D16" s="23"/>
       <c r="E16" s="27"/>
     </row>
-    <row r="17" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="17" spans="2:5" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="27"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:5">
       <c r="B18" s="29" t="s">
         <v>28</v>
       </c>
@@ -5645,7 +5654,7 @@
       <c r="D18" s="94"/>
       <c r="E18" s="30"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:5">
       <c r="B19" s="29"/>
       <c r="C19" s="101" t="s">
         <v>181</v>
@@ -5655,7 +5664,7 @@
       </c>
       <c r="E19" s="30"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:5">
       <c r="B20" s="29"/>
       <c r="C20" s="102" t="s">
         <v>165</v>
@@ -5665,7 +5674,7 @@
       </c>
       <c r="E20" s="30"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:5">
       <c r="B21" s="29"/>
       <c r="C21" s="102" t="s">
         <v>167</v>
@@ -5675,7 +5684,7 @@
       </c>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:5">
       <c r="B22" s="29"/>
       <c r="C22" s="102" t="s">
         <v>200</v>
@@ -5685,7 +5694,7 @@
       </c>
       <c r="E22" s="30"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:5">
       <c r="B23" s="29"/>
       <c r="C23" s="101" t="s">
         <v>202</v>
@@ -5695,7 +5704,7 @@
       </c>
       <c r="E23" s="30"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:5">
       <c r="B24" s="29"/>
       <c r="C24" s="101" t="s">
         <v>204</v>
@@ -5705,7 +5714,7 @@
       </c>
       <c r="E24" s="30"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:5">
       <c r="B25" s="29"/>
       <c r="C25" s="104" t="s">
         <v>240</v>
@@ -5715,7 +5724,7 @@
       </c>
       <c r="E25" s="30"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:5">
       <c r="B26" s="29"/>
       <c r="C26" s="104" t="s">
         <v>239</v>
@@ -5725,7 +5734,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:5">
       <c r="B27" s="29"/>
       <c r="C27" s="104" t="s">
         <v>202</v>
@@ -5735,18 +5744,18 @@
       </c>
       <c r="E27" s="30"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:5">
       <c r="B28" s="29"/>
       <c r="E28" s="30"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:5">
       <c r="B29" s="29"/>
       <c r="C29" s="1" t="s">
         <v>225</v>
       </c>
       <c r="E29" s="30"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:5">
       <c r="B30" s="29"/>
       <c r="C30" s="102" t="s">
         <v>165</v>
@@ -5756,7 +5765,7 @@
       </c>
       <c r="E30" s="30"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:5">
       <c r="B31" s="29"/>
       <c r="C31" s="102" t="s">
         <v>167</v>
@@ -5766,7 +5775,7 @@
       </c>
       <c r="E31" s="30"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:5">
       <c r="B32" s="29"/>
       <c r="C32" s="101" t="s">
         <v>202</v>
@@ -5776,7 +5785,7 @@
       </c>
       <c r="E32" s="30"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:5">
       <c r="B33" s="29"/>
       <c r="C33" t="s">
         <v>244</v>
@@ -5785,36 +5794,35 @@
         <v>246</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:5">
       <c r="B34" s="29"/>
       <c r="C34" t="s">
         <v>245</v>
       </c>
-      <c r="D34" s="107" t="s">
+      <c r="D34" t="s">
         <v>247</v>
       </c>
       <c r="E34" s="30" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:5">
       <c r="B35" s="29"/>
       <c r="C35" t="s">
         <v>249</v>
       </c>
-      <c r="D35" s="107" t="s">
+      <c r="D35" t="s">
         <v>248</v>
       </c>
       <c r="E35" s="30" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:5">
       <c r="B36" s="31"/>
-      <c r="D36" s="107"/>
       <c r="E36" s="30"/>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:5">
       <c r="B37" s="29" t="s">
         <v>29</v>
       </c>
@@ -5823,11 +5831,11 @@
       </c>
       <c r="E37" s="30"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:5">
       <c r="B38" s="31"/>
       <c r="E38" s="30"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:5">
       <c r="B39" s="29" t="s">
         <v>30</v>
       </c>
@@ -5836,11 +5844,11 @@
       </c>
       <c r="E39" s="30"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:5">
       <c r="B40" s="31"/>
       <c r="E40" s="30"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="41" spans="2:5">
       <c r="B41" s="29" t="s">
         <v>31</v>
       </c>
@@ -5849,11 +5857,11 @@
       </c>
       <c r="E41" s="30"/>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:5">
       <c r="B42" s="31"/>
       <c r="E42" s="30"/>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:5">
       <c r="B43" s="29" t="s">
         <v>32</v>
       </c>
@@ -5862,15 +5870,15 @@
       </c>
       <c r="E43" s="30"/>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:5">
       <c r="B44" s="29"/>
       <c r="E44" s="30"/>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="45" spans="2:5">
       <c r="B45" s="29"/>
       <c r="E45" s="30"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:5">
       <c r="B46" s="32" t="s">
         <v>33</v>
       </c>
@@ -5879,21 +5887,21 @@
       </c>
       <c r="E46" s="30"/>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:5">
       <c r="B47" s="34"/>
       <c r="C47" s="1" t="s">
         <v>190</v>
       </c>
       <c r="E47" s="30"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:5">
       <c r="B48" s="34"/>
       <c r="C48" s="33" t="s">
         <v>35</v>
       </c>
       <c r="E48" s="30"/>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="49" spans="2:5">
       <c r="B49" s="34"/>
       <c r="C49" s="100">
         <v>0.2</v>
@@ -5903,24 +5911,24 @@
       </c>
       <c r="E49" s="30"/>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="50" spans="2:5">
       <c r="B50" s="34"/>
       <c r="C50" s="33"/>
       <c r="E50" s="30"/>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="51" spans="2:5">
       <c r="B51" s="31"/>
       <c r="C51" s="33" t="s">
         <v>36</v>
       </c>
       <c r="E51" s="30"/>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="52" spans="2:5">
       <c r="B52" s="34"/>
       <c r="C52" s="33"/>
       <c r="E52" s="30"/>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="53" spans="2:5">
       <c r="B53" s="36"/>
       <c r="C53" s="37"/>
       <c r="D53" s="38"/>
@@ -5955,18 +5963,18 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="B1:E58"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="20.31640625" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:5">
       <c r="B1" s="1" t="s">
         <v>256</v>
       </c>
@@ -5974,7 +5982,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
         <v>89</v>
       </c>
@@ -5988,7 +5996,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:5">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -6002,7 +6010,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:5">
       <c r="B4" s="5" t="s">
         <v>261</v>
       </c>
@@ -6016,11 +6024,11 @@
         <v>262</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:5">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -6028,19 +6036,19 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B6" s="111" t="s">
+    <row r="6" spans="2:5">
+      <c r="B6" s="110" t="s">
         <v>266</v>
       </c>
-      <c r="C6" s="111"/>
+      <c r="C6" s="110"/>
       <c r="D6" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="E6" s="108" t="s">
+      <c r="E6" s="107" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:5">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -6054,7 +6062,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>141</v>
       </c>
@@ -6068,27 +6076,27 @@
         <v>264</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:5" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-    </row>
-    <row r="10" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+    </row>
+    <row r="10" spans="2:5" ht="13.5" customHeight="1">
       <c r="B10" s="17" t="s">
         <v>288</v>
       </c>
-      <c r="C10" s="113" t="s">
+      <c r="C10" s="114" t="s">
         <v>289</v>
       </c>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.1">
+      <c r="D10" s="114"/>
+      <c r="E10" s="114"/>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" s="18" t="s">
         <v>24</v>
       </c>
@@ -6096,21 +6104,21 @@
       <c r="D11" s="20"/>
       <c r="E11" s="21"/>
     </row>
-    <row r="12" spans="2:5" ht="93" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B12" s="114" t="s">
+    <row r="12" spans="2:5" ht="93" customHeight="1">
+      <c r="B12" s="113" t="s">
         <v>290</v>
       </c>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="114"/>
-    </row>
-    <row r="13" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+    </row>
+    <row r="13" spans="2:5" ht="16.5" customHeight="1">
       <c r="B13" s="22"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="24"/>
     </row>
-    <row r="14" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="14" spans="2:5" ht="16.5" customHeight="1">
       <c r="B14" s="25" t="s">
         <v>25</v>
       </c>
@@ -6120,7 +6128,7 @@
       <c r="D14" s="23"/>
       <c r="E14" s="27"/>
     </row>
-    <row r="15" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="15" spans="2:5" ht="16.5" customHeight="1">
       <c r="B15" s="25" t="s">
         <v>26</v>
       </c>
@@ -6128,7 +6136,7 @@
       <c r="D15" s="23"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="16" spans="2:5" ht="16.5" customHeight="1">
       <c r="B16" s="25" t="s">
         <v>27</v>
       </c>
@@ -6138,13 +6146,13 @@
       <c r="D16" s="23"/>
       <c r="E16" s="27"/>
     </row>
-    <row r="17" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="17" spans="2:5" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="27"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:5">
       <c r="B18" s="29" t="s">
         <v>28</v>
       </c>
@@ -6153,39 +6161,39 @@
       </c>
       <c r="E18" s="30"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:5">
       <c r="B19" s="29"/>
       <c r="C19" s="1" t="s">
         <v>270</v>
       </c>
       <c r="E19" s="30"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:5">
       <c r="B20" s="29"/>
       <c r="C20" t="s">
         <v>271</v>
       </c>
       <c r="E20" s="30"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:5">
       <c r="B21" s="29"/>
       <c r="C21" t="s">
         <v>272</v>
       </c>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:5">
       <c r="B22" s="29"/>
       <c r="E22" s="30"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:5">
       <c r="B23" s="29"/>
       <c r="C23" t="s">
         <v>273</v>
       </c>
       <c r="E23" s="30"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:5">
       <c r="B24" s="29"/>
       <c r="C24" t="s">
         <v>274</v>
@@ -6195,7 +6203,7 @@
       </c>
       <c r="E24" s="30"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:5">
       <c r="B25" s="29"/>
       <c r="C25" t="s">
         <v>275</v>
@@ -6205,15 +6213,15 @@
       </c>
       <c r="E25" s="30"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:5">
       <c r="B26" s="29"/>
       <c r="E26" s="30"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:5">
       <c r="B27" s="31"/>
       <c r="E27" s="30"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:5">
       <c r="B28" s="29" t="s">
         <v>29</v>
       </c>
@@ -6222,37 +6230,37 @@
       </c>
       <c r="E28" s="30"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:5">
       <c r="B29" s="29"/>
       <c r="E29" s="30"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:5">
       <c r="B30" s="31"/>
       <c r="C30" t="s">
         <v>279</v>
       </c>
       <c r="E30" s="30"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:5">
       <c r="B31" s="31"/>
       <c r="C31" t="s">
         <v>280</v>
       </c>
       <c r="E31" s="30"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:5">
       <c r="B32" s="31"/>
       <c r="E32" s="30"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:5">
       <c r="B33" s="31"/>
       <c r="E33" s="30"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:5">
       <c r="B34" s="31"/>
       <c r="E34" s="30"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:5">
       <c r="B35" s="29" t="s">
         <v>30</v>
       </c>
@@ -6261,26 +6269,26 @@
       </c>
       <c r="E35" s="30"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:5">
       <c r="B36" s="29"/>
       <c r="C36" t="s">
         <v>282</v>
       </c>
       <c r="E36" s="30"/>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:5">
       <c r="B37" s="29"/>
       <c r="E37" s="30"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:5">
       <c r="B38" s="29"/>
       <c r="E38" s="30"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:5">
       <c r="B39" s="31"/>
       <c r="E39" s="30"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:5">
       <c r="B40" s="29" t="s">
         <v>31</v>
       </c>
@@ -6289,23 +6297,23 @@
       </c>
       <c r="E40" s="30"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="41" spans="2:5">
       <c r="B41" s="31"/>
       <c r="E41" s="30"/>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:5">
       <c r="B42" s="31"/>
       <c r="E42" s="30"/>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:5">
       <c r="B43" s="31"/>
       <c r="E43" s="30"/>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:5">
       <c r="B44" s="31"/>
       <c r="E44" s="30"/>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="45" spans="2:5">
       <c r="B45" s="29" t="s">
         <v>32</v>
       </c>
@@ -6314,23 +6322,23 @@
       </c>
       <c r="E45" s="30"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:5">
       <c r="B46" s="29"/>
       <c r="E46" s="30"/>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:5">
       <c r="B47" s="29"/>
       <c r="E47" s="30"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:5">
       <c r="B48" s="31"/>
       <c r="E48" s="30"/>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="49" spans="2:5">
       <c r="B49" s="29"/>
       <c r="E49" s="30"/>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="50" spans="2:5">
       <c r="B50" s="32" t="s">
         <v>33</v>
       </c>
@@ -6339,56 +6347,56 @@
       </c>
       <c r="E50" s="30"/>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="51" spans="2:5">
       <c r="B51" s="34"/>
-      <c r="C51" s="109" t="s">
+      <c r="C51" s="108" t="s">
         <v>190</v>
       </c>
       <c r="E51" s="30"/>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="52" spans="2:5">
       <c r="B52" s="34"/>
       <c r="C52" s="33" t="s">
         <v>35</v>
       </c>
       <c r="E52" s="30"/>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="53" spans="2:5">
       <c r="B53" s="34"/>
       <c r="C53" s="100">
         <v>0.3</v>
       </c>
       <c r="E53" s="30"/>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="54" spans="2:5">
       <c r="B54" s="34"/>
       <c r="C54" s="33" t="s">
         <v>285</v>
       </c>
       <c r="E54" s="30"/>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="55" spans="2:5">
       <c r="B55" s="34"/>
       <c r="C55" s="33" t="s">
         <v>284</v>
       </c>
       <c r="E55" s="30"/>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="56" spans="2:5">
       <c r="B56" s="31"/>
       <c r="C56" s="33" t="s">
         <v>36</v>
       </c>
       <c r="E56" s="30"/>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="57" spans="2:5">
       <c r="B57" s="31"/>
       <c r="C57" s="33" t="s">
         <v>287</v>
       </c>
       <c r="E57" s="30"/>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="58" spans="2:5">
       <c r="B58" s="36"/>
       <c r="C58" s="37" t="s">
         <v>286</v>
@@ -6404,6 +6412,7 @@
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0B00-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -6420,29 +6429,20 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AACBE63-5FB8-6243-BE62-03803AB6D465}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="B1:E49"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="20.31640625" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:5">
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
@@ -6464,7 +6464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:5">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -6478,17 +6478,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:5">
       <c r="B4" s="5"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="7"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:5">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -6496,13 +6496,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
+    <row r="6" spans="2:5">
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
       <c r="D6" s="6"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:5">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -6516,7 +6516,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:5">
       <c r="B8" s="5"/>
       <c r="C8" s="13"/>
       <c r="D8" s="14" t="s">
@@ -6524,23 +6524,23 @@
       </c>
       <c r="E8" s="15"/>
     </row>
-    <row r="9" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:5" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-    </row>
-    <row r="10" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+    </row>
+    <row r="10" spans="2:5" ht="13.5" customHeight="1">
       <c r="B10" s="17"/>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.1">
+      <c r="C10" s="114"/>
+      <c r="D10" s="114"/>
+      <c r="E10" s="114"/>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" s="18" t="s">
         <v>24</v>
       </c>
@@ -6548,19 +6548,19 @@
       <c r="D11" s="20"/>
       <c r="E11" s="21"/>
     </row>
-    <row r="12" spans="2:5" ht="93" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B12" s="114"/>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="114"/>
-    </row>
-    <row r="13" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="12" spans="2:5" ht="93" customHeight="1">
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+    </row>
+    <row r="13" spans="2:5" ht="16.5" customHeight="1">
       <c r="B13" s="22"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="24"/>
     </row>
-    <row r="14" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="14" spans="2:5" ht="16.5" customHeight="1">
       <c r="B14" s="25" t="s">
         <v>25</v>
       </c>
@@ -6568,7 +6568,7 @@
       <c r="D14" s="23"/>
       <c r="E14" s="27"/>
     </row>
-    <row r="15" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="15" spans="2:5" ht="16.5" customHeight="1">
       <c r="B15" s="25" t="s">
         <v>26</v>
       </c>
@@ -6576,7 +6576,7 @@
       <c r="D15" s="23"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="16" spans="2:5" ht="16.5" customHeight="1">
       <c r="B16" s="25" t="s">
         <v>27</v>
       </c>
@@ -6584,129 +6584,129 @@
       <c r="D16" s="23"/>
       <c r="E16" s="27"/>
     </row>
-    <row r="17" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="17" spans="2:5" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="27"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:5">
       <c r="B18" s="29" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="1"/>
       <c r="E18" s="30"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:5">
       <c r="B19" s="29"/>
       <c r="C19" s="1"/>
       <c r="E19" s="30"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:5">
       <c r="B20" s="29"/>
       <c r="E20" s="30"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:5">
       <c r="B21" s="29"/>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:5">
       <c r="B22" s="31"/>
       <c r="E22" s="30"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:5">
       <c r="B23" s="29" t="s">
         <v>29</v>
       </c>
       <c r="E23" s="30"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:5">
       <c r="B24" s="31"/>
       <c r="E24" s="30"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:5">
       <c r="B25" s="31"/>
       <c r="E25" s="30"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:5">
       <c r="B26" s="31"/>
       <c r="E26" s="30"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:5">
       <c r="B27" s="31"/>
       <c r="E27" s="30"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:5">
       <c r="B28" s="31"/>
       <c r="E28" s="30"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:5">
       <c r="B29" s="29" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="30"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:5">
       <c r="B30" s="29"/>
       <c r="E30" s="30"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:5">
       <c r="B31" s="29"/>
       <c r="E31" s="30"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:5">
       <c r="B32" s="29"/>
       <c r="E32" s="30"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:5">
       <c r="B33" s="31"/>
       <c r="E33" s="30"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:5">
       <c r="B34" s="29" t="s">
         <v>31</v>
       </c>
       <c r="E34" s="30"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:5">
       <c r="B35" s="31"/>
       <c r="E35" s="30"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:5">
       <c r="B36" s="31"/>
       <c r="E36" s="30"/>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:5">
       <c r="B37" s="31"/>
       <c r="E37" s="30"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:5">
       <c r="B38" s="31"/>
       <c r="E38" s="30"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:5">
       <c r="B39" s="29" t="s">
         <v>32</v>
       </c>
       <c r="E39" s="30"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:5">
       <c r="B40" s="29"/>
       <c r="E40" s="30"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="41" spans="2:5">
       <c r="B41" s="29"/>
       <c r="E41" s="30"/>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:5">
       <c r="B42" s="31"/>
       <c r="E42" s="30"/>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:5">
       <c r="B43" s="29"/>
       <c r="E43" s="30"/>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:5">
       <c r="B44" s="32" t="s">
         <v>33</v>
       </c>
@@ -6715,31 +6715,31 @@
       </c>
       <c r="E44" s="30"/>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="45" spans="2:5">
       <c r="B45" s="34"/>
       <c r="C45" s="35"/>
       <c r="E45" s="30"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:5">
       <c r="B46" s="34"/>
       <c r="C46" s="33" t="s">
         <v>35</v>
       </c>
       <c r="E46" s="30"/>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:5">
       <c r="B47" s="34"/>
       <c r="C47" s="33"/>
       <c r="E47" s="30"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:5">
       <c r="B48" s="31"/>
       <c r="C48" s="33" t="s">
         <v>36</v>
       </c>
       <c r="E48" s="30"/>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="49" spans="2:5">
       <c r="B49" s="36"/>
       <c r="C49" s="37"/>
       <c r="D49" s="38"/>
@@ -6753,6 +6753,7 @@
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0C00-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -6768,21 +6769,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="B1:E49"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="20.31640625" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:5">
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
@@ -6790,7 +6791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
@@ -6804,7 +6805,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:5">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -6818,17 +6819,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:5">
       <c r="B4" s="5"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="7"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:5">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -6836,13 +6837,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
+    <row r="6" spans="2:5">
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
       <c r="D6" s="6"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:5">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -6856,7 +6857,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:5">
       <c r="B8" s="5"/>
       <c r="C8" s="13"/>
       <c r="D8" s="14" t="s">
@@ -6864,23 +6865,23 @@
       </c>
       <c r="E8" s="15"/>
     </row>
-    <row r="9" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:5" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-    </row>
-    <row r="10" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+    </row>
+    <row r="10" spans="2:5" ht="13.5" customHeight="1">
       <c r="B10" s="17"/>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.1">
+      <c r="C10" s="114"/>
+      <c r="D10" s="114"/>
+      <c r="E10" s="114"/>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" s="18" t="s">
         <v>24</v>
       </c>
@@ -6888,19 +6889,19 @@
       <c r="D11" s="20"/>
       <c r="E11" s="21"/>
     </row>
-    <row r="12" spans="2:5" ht="93" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B12" s="114"/>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="114"/>
-    </row>
-    <row r="13" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="12" spans="2:5" ht="93" customHeight="1">
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+    </row>
+    <row r="13" spans="2:5" ht="16.5" customHeight="1">
       <c r="B13" s="22"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="24"/>
     </row>
-    <row r="14" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="14" spans="2:5" ht="16.5" customHeight="1">
       <c r="B14" s="25" t="s">
         <v>25</v>
       </c>
@@ -6908,7 +6909,7 @@
       <c r="D14" s="23"/>
       <c r="E14" s="27"/>
     </row>
-    <row r="15" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="15" spans="2:5" ht="16.5" customHeight="1">
       <c r="B15" s="25" t="s">
         <v>26</v>
       </c>
@@ -6916,7 +6917,7 @@
       <c r="D15" s="23"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="16" spans="2:5" ht="16.5" customHeight="1">
       <c r="B16" s="25" t="s">
         <v>27</v>
       </c>
@@ -6924,129 +6925,129 @@
       <c r="D16" s="23"/>
       <c r="E16" s="27"/>
     </row>
-    <row r="17" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="17" spans="2:5" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="27"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:5">
       <c r="B18" s="29" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="1"/>
       <c r="E18" s="30"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:5">
       <c r="B19" s="29"/>
       <c r="C19" s="1"/>
       <c r="E19" s="30"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:5">
       <c r="B20" s="29"/>
       <c r="E20" s="30"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:5">
       <c r="B21" s="29"/>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:5">
       <c r="B22" s="31"/>
       <c r="E22" s="30"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:5">
       <c r="B23" s="29" t="s">
         <v>29</v>
       </c>
       <c r="E23" s="30"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:5">
       <c r="B24" s="31"/>
       <c r="E24" s="30"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:5">
       <c r="B25" s="31"/>
       <c r="E25" s="30"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:5">
       <c r="B26" s="31"/>
       <c r="E26" s="30"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:5">
       <c r="B27" s="31"/>
       <c r="E27" s="30"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:5">
       <c r="B28" s="31"/>
       <c r="E28" s="30"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:5">
       <c r="B29" s="29" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="30"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:5">
       <c r="B30" s="29"/>
       <c r="E30" s="30"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:5">
       <c r="B31" s="29"/>
       <c r="E31" s="30"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:5">
       <c r="B32" s="29"/>
       <c r="E32" s="30"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:5">
       <c r="B33" s="31"/>
       <c r="E33" s="30"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:5">
       <c r="B34" s="29" t="s">
         <v>31</v>
       </c>
       <c r="E34" s="30"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:5">
       <c r="B35" s="31"/>
       <c r="E35" s="30"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:5">
       <c r="B36" s="31"/>
       <c r="E36" s="30"/>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:5">
       <c r="B37" s="31"/>
       <c r="E37" s="30"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:5">
       <c r="B38" s="31"/>
       <c r="E38" s="30"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:5">
       <c r="B39" s="29" t="s">
         <v>32</v>
       </c>
       <c r="E39" s="30"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:5">
       <c r="B40" s="29"/>
       <c r="E40" s="30"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="41" spans="2:5">
       <c r="B41" s="29"/>
       <c r="E41" s="30"/>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:5">
       <c r="B42" s="31"/>
       <c r="E42" s="30"/>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:5">
       <c r="B43" s="29"/>
       <c r="E43" s="30"/>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:5">
       <c r="B44" s="32" t="s">
         <v>33</v>
       </c>
@@ -7055,31 +7056,31 @@
       </c>
       <c r="E44" s="30"/>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="45" spans="2:5">
       <c r="B45" s="34"/>
       <c r="C45" s="35"/>
       <c r="E45" s="30"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:5">
       <c r="B46" s="34"/>
       <c r="C46" s="33" t="s">
         <v>35</v>
       </c>
       <c r="E46" s="30"/>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:5">
       <c r="B47" s="34"/>
       <c r="C47" s="33"/>
       <c r="E47" s="30"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:5">
       <c r="B48" s="31"/>
       <c r="C48" s="33" t="s">
         <v>36</v>
       </c>
       <c r="E48" s="30"/>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="49" spans="2:5">
       <c r="B49" s="36"/>
       <c r="C49" s="37"/>
       <c r="D49" s="38"/>
@@ -7093,6 +7094,7 @@
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0D00-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -7108,21 +7110,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="B1:E49"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="20.31640625" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:5">
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
@@ -7130,7 +7132,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
@@ -7144,7 +7146,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:5">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -7158,17 +7160,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:5">
       <c r="B4" s="5"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="7"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:5">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -7176,13 +7178,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
+    <row r="6" spans="2:5">
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
       <c r="D6" s="6"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:5">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -7196,7 +7198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:5">
       <c r="B8" s="5"/>
       <c r="C8" s="13"/>
       <c r="D8" s="14" t="s">
@@ -7204,23 +7206,23 @@
       </c>
       <c r="E8" s="15"/>
     </row>
-    <row r="9" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:5" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-    </row>
-    <row r="10" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+    </row>
+    <row r="10" spans="2:5" ht="13.5" customHeight="1">
       <c r="B10" s="17"/>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.1">
+      <c r="C10" s="114"/>
+      <c r="D10" s="114"/>
+      <c r="E10" s="114"/>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" s="18" t="s">
         <v>24</v>
       </c>
@@ -7228,19 +7230,19 @@
       <c r="D11" s="20"/>
       <c r="E11" s="21"/>
     </row>
-    <row r="12" spans="2:5" ht="93" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B12" s="114"/>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="114"/>
-    </row>
-    <row r="13" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="12" spans="2:5" ht="93" customHeight="1">
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+    </row>
+    <row r="13" spans="2:5" ht="16.5" customHeight="1">
       <c r="B13" s="22"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="24"/>
     </row>
-    <row r="14" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="14" spans="2:5" ht="16.5" customHeight="1">
       <c r="B14" s="25" t="s">
         <v>25</v>
       </c>
@@ -7248,7 +7250,7 @@
       <c r="D14" s="23"/>
       <c r="E14" s="27"/>
     </row>
-    <row r="15" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="15" spans="2:5" ht="16.5" customHeight="1">
       <c r="B15" s="25" t="s">
         <v>26</v>
       </c>
@@ -7256,7 +7258,7 @@
       <c r="D15" s="23"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="16" spans="2:5" ht="16.5" customHeight="1">
       <c r="B16" s="25" t="s">
         <v>27</v>
       </c>
@@ -7264,129 +7266,129 @@
       <c r="D16" s="23"/>
       <c r="E16" s="27"/>
     </row>
-    <row r="17" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="17" spans="2:5" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="27"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:5">
       <c r="B18" s="29" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="1"/>
       <c r="E18" s="30"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:5">
       <c r="B19" s="29"/>
       <c r="C19" s="1"/>
       <c r="E19" s="30"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:5">
       <c r="B20" s="29"/>
       <c r="E20" s="30"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:5">
       <c r="B21" s="29"/>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:5">
       <c r="B22" s="31"/>
       <c r="E22" s="30"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:5">
       <c r="B23" s="29" t="s">
         <v>29</v>
       </c>
       <c r="E23" s="30"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:5">
       <c r="B24" s="31"/>
       <c r="E24" s="30"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:5">
       <c r="B25" s="31"/>
       <c r="E25" s="30"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:5">
       <c r="B26" s="31"/>
       <c r="E26" s="30"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:5">
       <c r="B27" s="31"/>
       <c r="E27" s="30"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:5">
       <c r="B28" s="31"/>
       <c r="E28" s="30"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:5">
       <c r="B29" s="29" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="30"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:5">
       <c r="B30" s="29"/>
       <c r="E30" s="30"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:5">
       <c r="B31" s="29"/>
       <c r="E31" s="30"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:5">
       <c r="B32" s="29"/>
       <c r="E32" s="30"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:5">
       <c r="B33" s="31"/>
       <c r="E33" s="30"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:5">
       <c r="B34" s="29" t="s">
         <v>31</v>
       </c>
       <c r="E34" s="30"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:5">
       <c r="B35" s="31"/>
       <c r="E35" s="30"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:5">
       <c r="B36" s="31"/>
       <c r="E36" s="30"/>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:5">
       <c r="B37" s="31"/>
       <c r="E37" s="30"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:5">
       <c r="B38" s="31"/>
       <c r="E38" s="30"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:5">
       <c r="B39" s="29" t="s">
         <v>32</v>
       </c>
       <c r="E39" s="30"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:5">
       <c r="B40" s="29"/>
       <c r="E40" s="30"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="41" spans="2:5">
       <c r="B41" s="29"/>
       <c r="E41" s="30"/>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:5">
       <c r="B42" s="31"/>
       <c r="E42" s="30"/>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:5">
       <c r="B43" s="29"/>
       <c r="E43" s="30"/>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:5">
       <c r="B44" s="32" t="s">
         <v>33</v>
       </c>
@@ -7395,31 +7397,31 @@
       </c>
       <c r="E44" s="30"/>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="45" spans="2:5">
       <c r="B45" s="34"/>
       <c r="C45" s="35"/>
       <c r="E45" s="30"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:5">
       <c r="B46" s="34"/>
       <c r="C46" s="33" t="s">
         <v>35</v>
       </c>
       <c r="E46" s="30"/>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:5">
       <c r="B47" s="34"/>
       <c r="C47" s="33"/>
       <c r="E47" s="30"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:5">
       <c r="B48" s="31"/>
       <c r="C48" s="33" t="s">
         <v>36</v>
       </c>
       <c r="E48" s="30"/>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="49" spans="2:5">
       <c r="B49" s="36"/>
       <c r="C49" s="37"/>
       <c r="D49" s="38"/>
@@ -7433,6 +7435,7 @@
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0E00-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -7448,21 +7451,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="B1:E49"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="20.31640625" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:5">
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
@@ -7470,7 +7473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
@@ -7484,7 +7487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:5">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -7498,17 +7501,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:5">
       <c r="B4" s="5"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="7"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:5">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -7516,13 +7519,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
+    <row r="6" spans="2:5">
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
       <c r="D6" s="6"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:5">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -7536,7 +7539,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:5">
       <c r="B8" s="5"/>
       <c r="C8" s="13"/>
       <c r="D8" s="14" t="s">
@@ -7544,23 +7547,23 @@
       </c>
       <c r="E8" s="15"/>
     </row>
-    <row r="9" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:5" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-    </row>
-    <row r="10" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+    </row>
+    <row r="10" spans="2:5" ht="13.5" customHeight="1">
       <c r="B10" s="17"/>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.1">
+      <c r="C10" s="114"/>
+      <c r="D10" s="114"/>
+      <c r="E10" s="114"/>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" s="18" t="s">
         <v>24</v>
       </c>
@@ -7568,19 +7571,19 @@
       <c r="D11" s="20"/>
       <c r="E11" s="21"/>
     </row>
-    <row r="12" spans="2:5" ht="93" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B12" s="114"/>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="114"/>
-    </row>
-    <row r="13" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="12" spans="2:5" ht="93" customHeight="1">
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+    </row>
+    <row r="13" spans="2:5" ht="16.5" customHeight="1">
       <c r="B13" s="22"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="24"/>
     </row>
-    <row r="14" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="14" spans="2:5" ht="16.5" customHeight="1">
       <c r="B14" s="25" t="s">
         <v>25</v>
       </c>
@@ -7588,7 +7591,7 @@
       <c r="D14" s="23"/>
       <c r="E14" s="27"/>
     </row>
-    <row r="15" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="15" spans="2:5" ht="16.5" customHeight="1">
       <c r="B15" s="25" t="s">
         <v>26</v>
       </c>
@@ -7596,7 +7599,7 @@
       <c r="D15" s="23"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="16" spans="2:5" ht="16.5" customHeight="1">
       <c r="B16" s="25" t="s">
         <v>27</v>
       </c>
@@ -7604,129 +7607,129 @@
       <c r="D16" s="23"/>
       <c r="E16" s="27"/>
     </row>
-    <row r="17" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="17" spans="2:5" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="27"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:5">
       <c r="B18" s="29" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="1"/>
       <c r="E18" s="30"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:5">
       <c r="B19" s="29"/>
       <c r="C19" s="1"/>
       <c r="E19" s="30"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:5">
       <c r="B20" s="29"/>
       <c r="E20" s="30"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:5">
       <c r="B21" s="29"/>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:5">
       <c r="B22" s="31"/>
       <c r="E22" s="30"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:5">
       <c r="B23" s="29" t="s">
         <v>29</v>
       </c>
       <c r="E23" s="30"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:5">
       <c r="B24" s="31"/>
       <c r="E24" s="30"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:5">
       <c r="B25" s="31"/>
       <c r="E25" s="30"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:5">
       <c r="B26" s="31"/>
       <c r="E26" s="30"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:5">
       <c r="B27" s="31"/>
       <c r="E27" s="30"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:5">
       <c r="B28" s="31"/>
       <c r="E28" s="30"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:5">
       <c r="B29" s="29" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="30"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:5">
       <c r="B30" s="29"/>
       <c r="E30" s="30"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:5">
       <c r="B31" s="29"/>
       <c r="E31" s="30"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:5">
       <c r="B32" s="29"/>
       <c r="E32" s="30"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:5">
       <c r="B33" s="31"/>
       <c r="E33" s="30"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:5">
       <c r="B34" s="29" t="s">
         <v>31</v>
       </c>
       <c r="E34" s="30"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:5">
       <c r="B35" s="31"/>
       <c r="E35" s="30"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:5">
       <c r="B36" s="31"/>
       <c r="E36" s="30"/>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:5">
       <c r="B37" s="31"/>
       <c r="E37" s="30"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:5">
       <c r="B38" s="31"/>
       <c r="E38" s="30"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:5">
       <c r="B39" s="29" t="s">
         <v>32</v>
       </c>
       <c r="E39" s="30"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:5">
       <c r="B40" s="29"/>
       <c r="E40" s="30"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="41" spans="2:5">
       <c r="B41" s="29"/>
       <c r="E41" s="30"/>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:5">
       <c r="B42" s="31"/>
       <c r="E42" s="30"/>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:5">
       <c r="B43" s="29"/>
       <c r="E43" s="30"/>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:5">
       <c r="B44" s="32" t="s">
         <v>33</v>
       </c>
@@ -7735,31 +7738,31 @@
       </c>
       <c r="E44" s="30"/>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="45" spans="2:5">
       <c r="B45" s="34"/>
       <c r="C45" s="35"/>
       <c r="E45" s="30"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:5">
       <c r="B46" s="34"/>
       <c r="C46" s="33" t="s">
         <v>35</v>
       </c>
       <c r="E46" s="30"/>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:5">
       <c r="B47" s="34"/>
       <c r="C47" s="33"/>
       <c r="E47" s="30"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:5">
       <c r="B48" s="31"/>
       <c r="C48" s="33" t="s">
         <v>36</v>
       </c>
       <c r="E48" s="30"/>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="49" spans="2:5">
       <c r="B49" s="36"/>
       <c r="C49" s="37"/>
       <c r="D49" s="38"/>
@@ -7773,6 +7776,7 @@
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0F00-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -7788,21 +7792,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="B1:E49"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="20.31640625" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:5">
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
@@ -7810,7 +7814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
@@ -7824,7 +7828,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:5">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -7838,17 +7842,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:5">
       <c r="B4" s="5"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="7"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:5">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -7856,13 +7860,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
+    <row r="6" spans="2:5">
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
       <c r="D6" s="6"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:5">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -7876,7 +7880,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:5">
       <c r="B8" s="5"/>
       <c r="C8" s="13"/>
       <c r="D8" s="14" t="s">
@@ -7884,23 +7888,23 @@
       </c>
       <c r="E8" s="15"/>
     </row>
-    <row r="9" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:5" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-    </row>
-    <row r="10" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+    </row>
+    <row r="10" spans="2:5" ht="13.5" customHeight="1">
       <c r="B10" s="17"/>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.1">
+      <c r="C10" s="114"/>
+      <c r="D10" s="114"/>
+      <c r="E10" s="114"/>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" s="18" t="s">
         <v>24</v>
       </c>
@@ -7908,19 +7912,19 @@
       <c r="D11" s="20"/>
       <c r="E11" s="21"/>
     </row>
-    <row r="12" spans="2:5" ht="93" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B12" s="114"/>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="114"/>
-    </row>
-    <row r="13" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="12" spans="2:5" ht="93" customHeight="1">
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+    </row>
+    <row r="13" spans="2:5" ht="16.5" customHeight="1">
       <c r="B13" s="22"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="24"/>
     </row>
-    <row r="14" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="14" spans="2:5" ht="16.5" customHeight="1">
       <c r="B14" s="25" t="s">
         <v>25</v>
       </c>
@@ -7928,7 +7932,7 @@
       <c r="D14" s="23"/>
       <c r="E14" s="27"/>
     </row>
-    <row r="15" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="15" spans="2:5" ht="16.5" customHeight="1">
       <c r="B15" s="25" t="s">
         <v>26</v>
       </c>
@@ -7936,7 +7940,7 @@
       <c r="D15" s="23"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="16" spans="2:5" ht="16.5" customHeight="1">
       <c r="B16" s="25" t="s">
         <v>27</v>
       </c>
@@ -7944,129 +7948,129 @@
       <c r="D16" s="23"/>
       <c r="E16" s="27"/>
     </row>
-    <row r="17" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="17" spans="2:5" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="27"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:5">
       <c r="B18" s="29" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="1"/>
       <c r="E18" s="30"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:5">
       <c r="B19" s="29"/>
       <c r="C19" s="1"/>
       <c r="E19" s="30"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:5">
       <c r="B20" s="29"/>
       <c r="E20" s="30"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:5">
       <c r="B21" s="29"/>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:5">
       <c r="B22" s="31"/>
       <c r="E22" s="30"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:5">
       <c r="B23" s="29" t="s">
         <v>29</v>
       </c>
       <c r="E23" s="30"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:5">
       <c r="B24" s="31"/>
       <c r="E24" s="30"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:5">
       <c r="B25" s="31"/>
       <c r="E25" s="30"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:5">
       <c r="B26" s="31"/>
       <c r="E26" s="30"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:5">
       <c r="B27" s="31"/>
       <c r="E27" s="30"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:5">
       <c r="B28" s="31"/>
       <c r="E28" s="30"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:5">
       <c r="B29" s="29" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="30"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:5">
       <c r="B30" s="29"/>
       <c r="E30" s="30"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:5">
       <c r="B31" s="29"/>
       <c r="E31" s="30"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:5">
       <c r="B32" s="29"/>
       <c r="E32" s="30"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:5">
       <c r="B33" s="31"/>
       <c r="E33" s="30"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:5">
       <c r="B34" s="29" t="s">
         <v>31</v>
       </c>
       <c r="E34" s="30"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:5">
       <c r="B35" s="31"/>
       <c r="E35" s="30"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:5">
       <c r="B36" s="31"/>
       <c r="E36" s="30"/>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:5">
       <c r="B37" s="31"/>
       <c r="E37" s="30"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:5">
       <c r="B38" s="31"/>
       <c r="E38" s="30"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:5">
       <c r="B39" s="29" t="s">
         <v>32</v>
       </c>
       <c r="E39" s="30"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:5">
       <c r="B40" s="29"/>
       <c r="E40" s="30"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="41" spans="2:5">
       <c r="B41" s="29"/>
       <c r="E41" s="30"/>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:5">
       <c r="B42" s="31"/>
       <c r="E42" s="30"/>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:5">
       <c r="B43" s="29"/>
       <c r="E43" s="30"/>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:5">
       <c r="B44" s="32" t="s">
         <v>33</v>
       </c>
@@ -8075,31 +8079,31 @@
       </c>
       <c r="E44" s="30"/>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="45" spans="2:5">
       <c r="B45" s="34"/>
       <c r="C45" s="35"/>
       <c r="E45" s="30"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:5">
       <c r="B46" s="34"/>
       <c r="C46" s="33" t="s">
         <v>35</v>
       </c>
       <c r="E46" s="30"/>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:5">
       <c r="B47" s="34"/>
       <c r="C47" s="33"/>
       <c r="E47" s="30"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:5">
       <c r="B48" s="31"/>
       <c r="C48" s="33" t="s">
         <v>36</v>
       </c>
       <c r="E48" s="30"/>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="49" spans="2:5">
       <c r="B49" s="36"/>
       <c r="C49" s="37"/>
       <c r="D49" s="38"/>
@@ -8113,6 +8117,7 @@
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-1000-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -8128,14 +8133,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1025" width="11.58984375" customWidth="1"/>
+    <col min="1" max="1025" width="11.625" customWidth="1"/>
   </cols>
   <sheetData/>
+  <phoneticPr fontId="33"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
@@ -8148,18 +8154,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:E49"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="20.31640625" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:5">
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
@@ -8167,7 +8173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
@@ -8181,7 +8187,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:5">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -8195,17 +8201,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:5">
       <c r="B4" s="5"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="7"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:5">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -8213,13 +8219,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
+    <row r="6" spans="2:5">
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
       <c r="D6" s="6"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:5">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -8233,7 +8239,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:5">
       <c r="B8" s="5"/>
       <c r="C8" s="13"/>
       <c r="D8" s="14" t="s">
@@ -8241,23 +8247,23 @@
       </c>
       <c r="E8" s="15"/>
     </row>
-    <row r="9" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:5" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-    </row>
-    <row r="10" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+    </row>
+    <row r="10" spans="2:5" ht="13.5" customHeight="1">
       <c r="B10" s="17"/>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.1">
+      <c r="C10" s="114"/>
+      <c r="D10" s="114"/>
+      <c r="E10" s="114"/>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" s="18" t="s">
         <v>24</v>
       </c>
@@ -8265,19 +8271,19 @@
       <c r="D11" s="20"/>
       <c r="E11" s="21"/>
     </row>
-    <row r="12" spans="2:5" ht="93" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B12" s="114"/>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="114"/>
-    </row>
-    <row r="13" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="12" spans="2:5" ht="93" customHeight="1">
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+    </row>
+    <row r="13" spans="2:5" ht="16.5" customHeight="1">
       <c r="B13" s="22"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="24"/>
     </row>
-    <row r="14" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="14" spans="2:5" ht="16.5" customHeight="1">
       <c r="B14" s="25" t="s">
         <v>25</v>
       </c>
@@ -8285,7 +8291,7 @@
       <c r="D14" s="23"/>
       <c r="E14" s="27"/>
     </row>
-    <row r="15" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="15" spans="2:5" ht="16.5" customHeight="1">
       <c r="B15" s="25" t="s">
         <v>26</v>
       </c>
@@ -8293,7 +8299,7 @@
       <c r="D15" s="23"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="16" spans="2:5" ht="16.5" customHeight="1">
       <c r="B16" s="25" t="s">
         <v>27</v>
       </c>
@@ -8301,129 +8307,129 @@
       <c r="D16" s="23"/>
       <c r="E16" s="27"/>
     </row>
-    <row r="17" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="17" spans="2:5" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="27"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:5">
       <c r="B18" s="29" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="1"/>
       <c r="E18" s="30"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:5">
       <c r="B19" s="29"/>
       <c r="C19" s="1"/>
       <c r="E19" s="30"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:5">
       <c r="B20" s="29"/>
       <c r="E20" s="30"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:5">
       <c r="B21" s="29"/>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:5">
       <c r="B22" s="31"/>
       <c r="E22" s="30"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:5">
       <c r="B23" s="29" t="s">
         <v>29</v>
       </c>
       <c r="E23" s="30"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:5">
       <c r="B24" s="31"/>
       <c r="E24" s="30"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:5">
       <c r="B25" s="31"/>
       <c r="E25" s="30"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:5">
       <c r="B26" s="31"/>
       <c r="E26" s="30"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:5">
       <c r="B27" s="31"/>
       <c r="E27" s="30"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:5">
       <c r="B28" s="31"/>
       <c r="E28" s="30"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:5">
       <c r="B29" s="29" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="30"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:5">
       <c r="B30" s="29"/>
       <c r="E30" s="30"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:5">
       <c r="B31" s="29"/>
       <c r="E31" s="30"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:5">
       <c r="B32" s="29"/>
       <c r="E32" s="30"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:5">
       <c r="B33" s="31"/>
       <c r="E33" s="30"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:5">
       <c r="B34" s="29" t="s">
         <v>31</v>
       </c>
       <c r="E34" s="30"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:5">
       <c r="B35" s="31"/>
       <c r="E35" s="30"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:5">
       <c r="B36" s="31"/>
       <c r="E36" s="30"/>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:5">
       <c r="B37" s="31"/>
       <c r="E37" s="30"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:5">
       <c r="B38" s="31"/>
       <c r="E38" s="30"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:5">
       <c r="B39" s="29" t="s">
         <v>32</v>
       </c>
       <c r="E39" s="30"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:5">
       <c r="B40" s="29"/>
       <c r="E40" s="30"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="41" spans="2:5">
       <c r="B41" s="29"/>
       <c r="E41" s="30"/>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:5">
       <c r="B42" s="31"/>
       <c r="E42" s="30"/>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:5">
       <c r="B43" s="29"/>
       <c r="E43" s="30"/>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:5">
       <c r="B44" s="32" t="s">
         <v>33</v>
       </c>
@@ -8432,31 +8438,31 @@
       </c>
       <c r="E44" s="30"/>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="45" spans="2:5">
       <c r="B45" s="34"/>
       <c r="C45" s="35"/>
       <c r="E45" s="30"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:5">
       <c r="B46" s="34"/>
       <c r="C46" s="33" t="s">
         <v>35</v>
       </c>
       <c r="E46" s="30"/>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:5">
       <c r="B47" s="34"/>
       <c r="C47" s="33"/>
       <c r="E47" s="30"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:5">
       <c r="B48" s="31"/>
       <c r="C48" s="33" t="s">
         <v>36</v>
       </c>
       <c r="E48" s="30"/>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="49" spans="2:5">
       <c r="B49" s="36"/>
       <c r="C49" s="37"/>
       <c r="D49" s="38"/>
@@ -8470,6 +8476,7 @@
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -8491,20 +8498,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B6:H79"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="17.31640625" style="40" customWidth="1"/>
-    <col min="3" max="4" width="1.76953125" customWidth="1"/>
-    <col min="5" max="5" width="16.2265625" customWidth="1"/>
-    <col min="6" max="6" width="20.31640625" customWidth="1"/>
-    <col min="7" max="7" width="25.76953125" customWidth="1"/>
-    <col min="8" max="8" width="32.04296875" customWidth="1"/>
-    <col min="9" max="9" width="1.2265625" customWidth="1"/>
-    <col min="10" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="17.375" style="40" customWidth="1"/>
+    <col min="3" max="4" width="1.75" customWidth="1"/>
+    <col min="5" max="5" width="16.25" customWidth="1"/>
+    <col min="6" max="6" width="20.375" customWidth="1"/>
+    <col min="7" max="7" width="25.75" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="1.25" customWidth="1"/>
+    <col min="10" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="6" spans="5:8">
       <c r="E6" s="41" t="s">
         <v>37</v>
       </c>
@@ -8512,7 +8519,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="7" spans="5:8">
       <c r="E7" s="1" t="s">
         <v>39</v>
       </c>
@@ -8526,7 +8533,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="8" spans="5:8">
       <c r="E8" s="2" t="s">
         <v>10</v>
       </c>
@@ -8540,7 +8547,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="9" spans="5:8">
       <c r="E9" s="5" t="s">
         <v>43</v>
       </c>
@@ -8554,11 +8561,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="5:8" x14ac:dyDescent="0.1">
-      <c r="E10" s="110" t="s">
+    <row r="10" spans="5:8">
+      <c r="E10" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="110"/>
+      <c r="F10" s="109"/>
       <c r="G10" s="8" t="s">
         <v>15</v>
       </c>
@@ -8566,11 +8573,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="5:8" x14ac:dyDescent="0.1">
-      <c r="E11" s="111" t="s">
+    <row r="11" spans="5:8">
+      <c r="E11" s="110" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="111"/>
+      <c r="F11" s="110"/>
       <c r="G11" s="6" t="s">
         <v>48</v>
       </c>
@@ -8578,7 +8585,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="12" spans="5:8">
       <c r="E12" s="42" t="s">
         <v>17</v>
       </c>
@@ -8592,7 +8599,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="13" spans="5:8">
       <c r="E13" s="43"/>
       <c r="F13" s="13"/>
       <c r="G13" s="14" t="s">
@@ -8602,27 +8609,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="5:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="14" spans="5:8" ht="13.5" customHeight="1">
       <c r="E14" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="112" t="s">
+      <c r="F14" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="112"/>
-      <c r="H14" s="112"/>
-    </row>
-    <row r="15" spans="5:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+    </row>
+    <row r="15" spans="5:8" ht="13.5" customHeight="1">
       <c r="E15" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="113" t="s">
+      <c r="F15" s="114" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="113"/>
-      <c r="H15" s="113"/>
-    </row>
-    <row r="16" spans="5:8" x14ac:dyDescent="0.1">
+      <c r="G15" s="114"/>
+      <c r="H15" s="114"/>
+    </row>
+    <row r="16" spans="5:8">
       <c r="E16" s="18" t="s">
         <v>24</v>
       </c>
@@ -8630,15 +8637,15 @@
       <c r="G16" s="20"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="5:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="E17" s="114" t="s">
+    <row r="17" spans="5:8" ht="32.25" customHeight="1">
+      <c r="E17" s="113" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="114"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="114"/>
-    </row>
-    <row r="18" spans="5:8" x14ac:dyDescent="0.1">
+      <c r="F17" s="113"/>
+      <c r="G17" s="113"/>
+      <c r="H17" s="113"/>
+    </row>
+    <row r="18" spans="5:8">
       <c r="E18" s="2" t="s">
         <v>10</v>
       </c>
@@ -8652,7 +8659,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="19" spans="5:8">
       <c r="E19" s="5" t="s">
         <v>54</v>
       </c>
@@ -8664,11 +8671,11 @@
       </c>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="5:8" x14ac:dyDescent="0.1">
-      <c r="E20" s="110" t="s">
+    <row r="20" spans="5:8">
+      <c r="E20" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="F20" s="110"/>
+      <c r="F20" s="109"/>
       <c r="G20" s="8" t="s">
         <v>15</v>
       </c>
@@ -8676,11 +8683,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="5:8" x14ac:dyDescent="0.1">
-      <c r="E21" s="111" t="s">
+    <row r="21" spans="5:8">
+      <c r="E21" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="F21" s="111"/>
+      <c r="F21" s="110"/>
       <c r="G21" s="43" t="s">
         <v>58</v>
       </c>
@@ -8688,27 +8695,27 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="5:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="22" spans="5:8" ht="13.5" customHeight="1">
       <c r="E22" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="F22" s="112" t="s">
+      <c r="F22" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="G22" s="112"/>
-      <c r="H22" s="112"/>
-    </row>
-    <row r="23" spans="5:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="G22" s="111"/>
+      <c r="H22" s="111"/>
+    </row>
+    <row r="23" spans="5:8" ht="13.5" customHeight="1">
       <c r="E23" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F23" s="115" t="s">
+      <c r="F23" s="112" t="s">
         <v>62</v>
       </c>
-      <c r="G23" s="115"/>
-      <c r="H23" s="115"/>
-    </row>
-    <row r="24" spans="5:8" x14ac:dyDescent="0.1">
+      <c r="G23" s="112"/>
+      <c r="H23" s="112"/>
+    </row>
+    <row r="24" spans="5:8">
       <c r="E24" s="18" t="s">
         <v>24</v>
       </c>
@@ -8716,21 +8723,21 @@
       <c r="G24" s="20"/>
       <c r="H24" s="21"/>
     </row>
-    <row r="25" spans="5:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="E25" s="114" t="s">
+    <row r="25" spans="5:8" ht="34.5" customHeight="1">
+      <c r="E25" s="113" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="114"/>
-      <c r="G25" s="114"/>
-      <c r="H25" s="114"/>
-    </row>
-    <row r="26" spans="5:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="F25" s="113"/>
+      <c r="G25" s="113"/>
+      <c r="H25" s="113"/>
+    </row>
+    <row r="26" spans="5:8" ht="16.5" customHeight="1">
       <c r="E26" s="22"/>
       <c r="F26" s="23"/>
       <c r="G26" s="23"/>
       <c r="H26" s="24"/>
     </row>
-    <row r="27" spans="5:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="27" spans="5:8" ht="16.5" customHeight="1">
       <c r="E27" s="25" t="s">
         <v>25</v>
       </c>
@@ -8740,7 +8747,7 @@
       <c r="G27" s="23"/>
       <c r="H27" s="27"/>
     </row>
-    <row r="28" spans="5:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="28" spans="5:8" ht="16.5" customHeight="1">
       <c r="E28" s="25" t="s">
         <v>26</v>
       </c>
@@ -8750,7 +8757,7 @@
       <c r="G28" s="23"/>
       <c r="H28" s="27"/>
     </row>
-    <row r="29" spans="5:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="29" spans="5:8" ht="16.5" customHeight="1">
       <c r="E29" s="47" t="s">
         <v>27</v>
       </c>
@@ -8760,13 +8767,13 @@
       <c r="G29" s="23"/>
       <c r="H29" s="27"/>
     </row>
-    <row r="30" spans="5:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="30" spans="5:8" ht="16.5" customHeight="1">
       <c r="E30" s="28"/>
       <c r="F30" s="23"/>
       <c r="G30" s="23"/>
       <c r="H30" s="27"/>
     </row>
-    <row r="31" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="31" spans="5:8">
       <c r="E31" s="29" t="s">
         <v>28</v>
       </c>
@@ -8775,54 +8782,54 @@
       </c>
       <c r="H31" s="30"/>
     </row>
-    <row r="32" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="32" spans="5:8">
       <c r="E32" s="29"/>
       <c r="F32" s="1" t="s">
         <v>67</v>
       </c>
       <c r="H32" s="30"/>
     </row>
-    <row r="33" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="33" spans="5:8">
       <c r="E33" s="29"/>
       <c r="F33" t="s">
         <v>68</v>
       </c>
       <c r="H33" s="30"/>
     </row>
-    <row r="34" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="34" spans="5:8">
       <c r="E34" s="29"/>
       <c r="H34" s="30"/>
     </row>
-    <row r="35" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="35" spans="5:8">
       <c r="E35" s="31"/>
       <c r="F35" t="s">
         <v>54</v>
       </c>
       <c r="H35" s="30"/>
     </row>
-    <row r="36" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="36" spans="5:8">
       <c r="E36" s="31"/>
       <c r="F36" t="s">
         <v>69</v>
       </c>
       <c r="H36" s="30"/>
     </row>
-    <row r="37" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="37" spans="5:8">
       <c r="E37" s="31"/>
       <c r="F37" t="s">
         <v>70</v>
       </c>
       <c r="H37" s="30"/>
     </row>
-    <row r="38" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="38" spans="5:8">
       <c r="E38" s="31"/>
       <c r="H38" s="30"/>
     </row>
-    <row r="39" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="39" spans="5:8">
       <c r="E39" s="31"/>
       <c r="H39" s="30"/>
     </row>
-    <row r="40" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="40" spans="5:8">
       <c r="E40" s="29" t="s">
         <v>29</v>
       </c>
@@ -8831,47 +8838,47 @@
       </c>
       <c r="H40" s="30"/>
     </row>
-    <row r="41" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="41" spans="5:8">
       <c r="E41" s="31"/>
       <c r="F41" t="s">
         <v>71</v>
       </c>
       <c r="H41" s="30"/>
     </row>
-    <row r="42" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="42" spans="5:8">
       <c r="E42" s="31"/>
       <c r="H42" s="30"/>
     </row>
-    <row r="43" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="43" spans="5:8">
       <c r="E43" s="31"/>
       <c r="F43" t="s">
         <v>54</v>
       </c>
       <c r="H43" s="30"/>
     </row>
-    <row r="44" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="44" spans="5:8">
       <c r="E44" s="29"/>
       <c r="F44" s="1" t="s">
         <v>72</v>
       </c>
       <c r="H44" s="30"/>
     </row>
-    <row r="45" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="45" spans="5:8">
       <c r="E45" s="29"/>
       <c r="F45" s="1" t="s">
         <v>73</v>
       </c>
       <c r="H45" s="30"/>
     </row>
-    <row r="46" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="46" spans="5:8">
       <c r="E46" s="31"/>
       <c r="H46" s="30"/>
     </row>
-    <row r="47" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="47" spans="5:8">
       <c r="E47" s="31"/>
       <c r="H47" s="30"/>
     </row>
-    <row r="48" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="48" spans="5:8">
       <c r="E48" s="29" t="s">
         <v>30</v>
       </c>
@@ -8880,43 +8887,43 @@
       </c>
       <c r="H48" s="30"/>
     </row>
-    <row r="49" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="49" spans="5:8">
       <c r="E49" s="29"/>
       <c r="F49" t="s">
         <v>71</v>
       </c>
       <c r="H49" s="30"/>
     </row>
-    <row r="50" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="50" spans="5:8">
       <c r="E50" s="31"/>
       <c r="F50" t="s">
         <v>54</v>
       </c>
       <c r="H50" s="30"/>
     </row>
-    <row r="51" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="51" spans="5:8">
       <c r="E51" s="31"/>
       <c r="F51" s="1" t="s">
         <v>74</v>
       </c>
       <c r="H51" s="30"/>
     </row>
-    <row r="52" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="52" spans="5:8">
       <c r="E52" s="31"/>
       <c r="F52" s="1" t="s">
         <v>75</v>
       </c>
       <c r="H52" s="30"/>
     </row>
-    <row r="53" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="53" spans="5:8">
       <c r="E53" s="31"/>
       <c r="H53" s="30"/>
     </row>
-    <row r="54" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="54" spans="5:8">
       <c r="E54" s="31"/>
       <c r="H54" s="30"/>
     </row>
-    <row r="55" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="55" spans="5:8">
       <c r="E55" s="29" t="s">
         <v>31</v>
       </c>
@@ -8925,29 +8932,29 @@
       </c>
       <c r="H55" s="30"/>
     </row>
-    <row r="56" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="56" spans="5:8">
       <c r="E56" s="29"/>
       <c r="F56" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H56" s="30"/>
     </row>
-    <row r="57" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="57" spans="5:8">
       <c r="E57" s="31"/>
       <c r="F57" t="s">
         <v>77</v>
       </c>
       <c r="H57" s="30"/>
     </row>
-    <row r="58" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="58" spans="5:8">
       <c r="E58" s="31"/>
       <c r="H58" s="30"/>
     </row>
-    <row r="59" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="59" spans="5:8">
       <c r="E59" s="31"/>
       <c r="H59" s="30"/>
     </row>
-    <row r="60" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="60" spans="5:8">
       <c r="E60" s="29" t="s">
         <v>32</v>
       </c>
@@ -8956,36 +8963,36 @@
       </c>
       <c r="H60" s="30"/>
     </row>
-    <row r="61" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="61" spans="5:8">
       <c r="E61" s="29"/>
       <c r="F61" t="s">
         <v>78</v>
       </c>
       <c r="H61" s="30"/>
     </row>
-    <row r="62" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="62" spans="5:8">
       <c r="E62" s="29"/>
       <c r="H62" s="30"/>
     </row>
-    <row r="63" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="63" spans="5:8">
       <c r="E63" s="31"/>
       <c r="F63" t="s">
         <v>54</v>
       </c>
       <c r="H63" s="30"/>
     </row>
-    <row r="64" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="64" spans="5:8">
       <c r="E64" s="31"/>
       <c r="F64" t="s">
         <v>79</v>
       </c>
       <c r="H64" s="30"/>
     </row>
-    <row r="65" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="65" spans="5:8">
       <c r="E65" s="31"/>
       <c r="H65" s="30"/>
     </row>
-    <row r="66" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="66" spans="5:8">
       <c r="E66" s="32" t="s">
         <v>33</v>
       </c>
@@ -8995,7 +9002,7 @@
       <c r="G66" s="33"/>
       <c r="H66" s="30"/>
     </row>
-    <row r="67" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="67" spans="5:8">
       <c r="E67" s="32"/>
       <c r="F67" s="33" t="s">
         <v>80</v>
@@ -9003,7 +9010,7 @@
       <c r="G67" s="33"/>
       <c r="H67" s="30"/>
     </row>
-    <row r="68" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="68" spans="5:8">
       <c r="E68" s="32"/>
       <c r="F68" s="33" t="s">
         <v>81</v>
@@ -9011,13 +9018,13 @@
       <c r="G68" s="33"/>
       <c r="H68" s="30"/>
     </row>
-    <row r="69" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="69" spans="5:8">
       <c r="E69" s="32"/>
       <c r="F69" s="33"/>
       <c r="G69" s="33"/>
       <c r="H69" s="30"/>
     </row>
-    <row r="70" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="70" spans="5:8">
       <c r="E70" s="32"/>
       <c r="F70" s="33" t="s">
         <v>35</v>
@@ -9025,7 +9032,7 @@
       <c r="G70" s="33"/>
       <c r="H70" s="30"/>
     </row>
-    <row r="71" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="71" spans="5:8">
       <c r="E71" s="32"/>
       <c r="F71" s="33" t="s">
         <v>82</v>
@@ -9033,7 +9040,7 @@
       <c r="G71" s="33"/>
       <c r="H71" s="30"/>
     </row>
-    <row r="72" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="72" spans="5:8">
       <c r="E72" s="32"/>
       <c r="F72" s="33" t="s">
         <v>83</v>
@@ -9041,7 +9048,7 @@
       <c r="G72" s="33"/>
       <c r="H72" s="30"/>
     </row>
-    <row r="73" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="73" spans="5:8">
       <c r="E73" s="32"/>
       <c r="F73" s="33" t="s">
         <v>84</v>
@@ -9049,13 +9056,13 @@
       <c r="G73" s="33"/>
       <c r="H73" s="30"/>
     </row>
-    <row r="74" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="74" spans="5:8">
       <c r="E74" s="32"/>
       <c r="F74" s="33"/>
       <c r="G74" s="33"/>
       <c r="H74" s="30"/>
     </row>
-    <row r="75" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="75" spans="5:8">
       <c r="E75" s="32"/>
       <c r="F75" s="33" t="s">
         <v>36</v>
@@ -9063,7 +9070,7 @@
       <c r="G75" s="33"/>
       <c r="H75" s="30"/>
     </row>
-    <row r="76" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="76" spans="5:8">
       <c r="E76" s="32"/>
       <c r="F76" s="33" t="s">
         <v>85</v>
@@ -9071,7 +9078,7 @@
       <c r="G76" s="33"/>
       <c r="H76" s="30"/>
     </row>
-    <row r="77" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="77" spans="5:8">
       <c r="E77" s="32"/>
       <c r="F77" s="33" t="s">
         <v>86</v>
@@ -9079,13 +9086,13 @@
       <c r="G77" s="33"/>
       <c r="H77" s="30"/>
     </row>
-    <row r="78" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="78" spans="5:8">
       <c r="E78" s="32"/>
       <c r="F78" s="33"/>
       <c r="G78" s="33"/>
       <c r="H78" s="30"/>
     </row>
-    <row r="79" spans="5:8" x14ac:dyDescent="0.1">
+    <row r="79" spans="5:8">
       <c r="E79" s="49"/>
       <c r="F79" s="37"/>
       <c r="G79" s="37"/>
@@ -9104,6 +9111,7 @@
     <mergeCell ref="F23:H23"/>
     <mergeCell ref="E25:H25"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="E13" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -9123,18 +9131,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:K73"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="20.31640625" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:10">
       <c r="B1" s="1" t="s">
         <v>87</v>
       </c>
@@ -9142,7 +9150,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:10">
       <c r="B2" s="1" t="s">
         <v>89</v>
       </c>
@@ -9156,7 +9164,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:10">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -9170,7 +9178,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:10">
       <c r="B4" s="5"/>
       <c r="C4" s="43" t="s">
         <v>93</v>
@@ -9180,11 +9188,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:10">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -9192,15 +9200,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.1">
-      <c r="B6" s="111" t="s">
+    <row r="6" spans="2:10">
+      <c r="B6" s="110" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="111"/>
+      <c r="C6" s="110"/>
       <c r="D6" s="6"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:10">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -9214,7 +9222,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:10">
       <c r="B8" s="5" t="s">
         <v>96</v>
       </c>
@@ -9226,27 +9234,27 @@
       </c>
       <c r="E8" s="15"/>
     </row>
-    <row r="9" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:10" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-    </row>
-    <row r="10" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+    </row>
+    <row r="10" spans="2:10" ht="13.5" customHeight="1">
       <c r="B10" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="118" t="s">
+      <c r="C10" s="117" t="s">
         <v>99</v>
       </c>
-      <c r="D10" s="118"/>
-      <c r="E10" s="118"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.1">
+      <c r="D10" s="117"/>
+      <c r="E10" s="117"/>
+    </row>
+    <row r="11" spans="2:10">
       <c r="B11" s="50" t="s">
         <v>24</v>
       </c>
@@ -9254,22 +9262,22 @@
       <c r="D11" s="20"/>
       <c r="E11" s="21"/>
     </row>
-    <row r="12" spans="2:10" ht="96" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B12" s="119" t="s">
+    <row r="12" spans="2:10" ht="96" customHeight="1">
+      <c r="B12" s="118" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="119"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
-    </row>
-    <row r="13" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+    </row>
+    <row r="13" spans="2:10" ht="16.5" customHeight="1">
       <c r="B13" s="22"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="24"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="14" spans="2:10" ht="16.5" customHeight="1">
       <c r="B14" s="25" t="s">
         <v>25</v>
       </c>
@@ -9281,7 +9289,7 @@
       <c r="G14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="15" spans="2:10" ht="16.5" customHeight="1">
       <c r="B15" s="25" t="s">
         <v>26</v>
       </c>
@@ -9292,7 +9300,7 @@
       <c r="E15" s="52"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="16" spans="2:10" ht="16.5" customHeight="1">
       <c r="B16" s="25" t="s">
         <v>27</v>
       </c>
@@ -9303,14 +9311,14 @@
       <c r="E16" s="52"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="17" spans="2:11" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="51"/>
       <c r="D17" s="51"/>
       <c r="E17" s="52"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:11">
       <c r="B18" s="29" t="s">
         <v>28</v>
       </c>
@@ -9321,14 +9329,14 @@
       <c r="E18" s="55"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:11">
       <c r="B19" s="29"/>
       <c r="C19" s="54"/>
       <c r="D19" s="54"/>
       <c r="E19" s="55"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:11" ht="15.6" customHeight="1">
       <c r="B20" s="29"/>
       <c r="C20" s="54" t="s">
         <v>104</v>
@@ -9338,7 +9346,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="58"/>
     </row>
-    <row r="21" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:11" ht="15.6" customHeight="1">
       <c r="B21" s="29"/>
       <c r="C21" s="59"/>
       <c r="D21" s="56"/>
@@ -9346,7 +9354,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="58"/>
     </row>
-    <row r="22" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:11" ht="15" customHeight="1">
       <c r="B22" s="29" t="s">
         <v>29</v>
       </c>
@@ -9358,7 +9366,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="58"/>
     </row>
-    <row r="23" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:11" ht="15" customHeight="1">
       <c r="B23" s="29"/>
       <c r="C23" s="54" t="s">
         <v>106</v>
@@ -9368,7 +9376,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="58"/>
     </row>
-    <row r="24" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:11" ht="15" customHeight="1">
       <c r="B24" s="29"/>
       <c r="C24" s="56" t="s">
         <v>107</v>
@@ -9378,7 +9386,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="58"/>
     </row>
-    <row r="25" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:11" ht="15.75">
       <c r="B25" s="29"/>
       <c r="C25" s="60" t="s">
         <v>108</v>
@@ -9388,7 +9396,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="58"/>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:11" ht="15" customHeight="1">
       <c r="B26" s="29"/>
       <c r="C26" s="63" t="s">
         <v>109</v>
@@ -9397,7 +9405,7 @@
       <c r="E26" s="62"/>
       <c r="K26" s="58"/>
     </row>
-    <row r="27" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:11" ht="15" customHeight="1">
       <c r="B27" s="29"/>
       <c r="C27" s="60" t="s">
         <v>110</v>
@@ -9406,20 +9414,20 @@
       <c r="E27" s="62"/>
       <c r="K27" s="58"/>
     </row>
-    <row r="28" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:11" ht="15" customHeight="1">
       <c r="B28" s="29"/>
       <c r="C28" s="56"/>
       <c r="D28" s="64"/>
       <c r="E28" s="62"/>
       <c r="K28" s="58"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:11">
       <c r="B29" s="31"/>
       <c r="C29" s="54"/>
       <c r="D29" s="61"/>
       <c r="E29" s="62"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:11">
       <c r="B30" s="29" t="s">
         <v>30</v>
       </c>
@@ -9429,13 +9437,13 @@
       <c r="D30" s="54"/>
       <c r="E30" s="55"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:11">
       <c r="B31" s="29"/>
       <c r="C31" s="56"/>
       <c r="D31" s="56"/>
       <c r="E31" s="57"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:11">
       <c r="B32" s="29" t="s">
         <v>31</v>
       </c>
@@ -9446,13 +9454,13 @@
       <c r="E32" s="57"/>
       <c r="J32" s="1"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:10">
       <c r="B33" s="29"/>
       <c r="C33" s="56"/>
       <c r="D33" s="56"/>
       <c r="E33" s="57"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:10">
       <c r="B34" s="29" t="s">
         <v>32</v>
       </c>
@@ -9460,19 +9468,19 @@
       <c r="D34" s="54"/>
       <c r="E34" s="55"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:10">
       <c r="B35" s="29"/>
       <c r="C35" s="54"/>
       <c r="D35" s="54"/>
       <c r="E35" s="55"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:10">
       <c r="B36" s="29"/>
       <c r="C36" s="54"/>
       <c r="D36" s="54"/>
       <c r="E36" s="55"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:10">
       <c r="B37" s="32" t="s">
         <v>33</v>
       </c>
@@ -9482,7 +9490,7 @@
       <c r="D37" s="54"/>
       <c r="E37" s="55"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:10">
       <c r="B38" s="34"/>
       <c r="C38" s="56" t="s">
         <v>113</v>
@@ -9490,7 +9498,7 @@
       <c r="D38" s="54"/>
       <c r="E38" s="55"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:10">
       <c r="B39" s="34"/>
       <c r="C39" s="56" t="s">
         <v>35</v>
@@ -9498,19 +9506,19 @@
       <c r="D39" s="54"/>
       <c r="E39" s="55"/>
     </row>
-    <row r="40" spans="2:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:10" ht="15.6" customHeight="1">
       <c r="B40" s="34"/>
-      <c r="C40" s="116"/>
-      <c r="D40" s="116"/>
-      <c r="E40" s="116"/>
-    </row>
-    <row r="41" spans="2:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="C40" s="115"/>
+      <c r="D40" s="115"/>
+      <c r="E40" s="115"/>
+    </row>
+    <row r="41" spans="2:10" ht="15.6" customHeight="1">
       <c r="B41" s="31"/>
       <c r="C41" s="65"/>
       <c r="D41" s="66"/>
       <c r="E41" s="67"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:10">
       <c r="B42" s="31"/>
       <c r="C42" s="56" t="s">
         <v>36</v>
@@ -9518,7 +9526,7 @@
       <c r="D42" s="54"/>
       <c r="E42" s="55"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:10">
       <c r="B43" s="31"/>
       <c r="C43" s="54" t="s">
         <v>113</v>
@@ -9527,14 +9535,14 @@
       <c r="E43" s="55"/>
       <c r="J43" s="1"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:10">
       <c r="B44" s="34"/>
       <c r="C44" s="56"/>
       <c r="D44" s="54"/>
       <c r="E44" s="55"/>
       <c r="J44" s="1"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="45" spans="2:10">
       <c r="B45" s="34"/>
       <c r="C45" s="56"/>
       <c r="D45" s="54"/>
@@ -9542,35 +9550,35 @@
       <c r="G45" s="1"/>
       <c r="J45" s="1"/>
     </row>
-    <row r="46" spans="2:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:10" ht="13.15" customHeight="1">
       <c r="B46" s="31"/>
       <c r="C46" s="56"/>
       <c r="D46" s="54"/>
       <c r="E46" s="55"/>
       <c r="J46" s="1"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:10">
       <c r="B47" s="31"/>
       <c r="C47" s="56"/>
       <c r="D47" s="54"/>
       <c r="E47" s="55"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:10">
       <c r="B48" s="31"/>
       <c r="C48" s="56"/>
       <c r="D48" s="54"/>
       <c r="E48" s="55"/>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="49" spans="2:10">
       <c r="B49" s="31"/>
       <c r="C49" s="54"/>
       <c r="D49" s="54"/>
       <c r="E49" s="55"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="50" spans="2:10">
       <c r="B50" s="31"/>
       <c r="C50" s="54"/>
       <c r="D50" s="54"/>
@@ -9578,43 +9586,43 @@
       <c r="G50" s="1"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="51" spans="2:10">
       <c r="B51" s="31"/>
       <c r="C51" s="54"/>
       <c r="D51" s="54"/>
       <c r="E51" s="55"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="52" spans="2:10">
       <c r="B52" s="31"/>
       <c r="C52" s="54"/>
       <c r="D52" s="54"/>
       <c r="E52" s="55"/>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="53" spans="2:10">
       <c r="B53" s="36"/>
       <c r="C53" s="68"/>
       <c r="D53" s="69"/>
       <c r="E53" s="70"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="54" spans="2:10">
       <c r="J54" s="1"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="55" spans="2:10">
       <c r="J55" s="1"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="56" spans="2:10">
       <c r="J56" s="1"/>
     </row>
-    <row r="57" spans="2:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="57" spans="2:10" ht="13.15" customHeight="1">
       <c r="G57" s="1"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.1">
+    <row r="72" spans="3:4">
       <c r="D72" s="1"/>
     </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.1">
+    <row r="73" spans="3:4">
       <c r="C73" s="33"/>
       <c r="D73" s="1"/>
     </row>
@@ -9627,6 +9635,7 @@
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -9645,18 +9654,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:K77"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="20.31640625" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:10">
       <c r="B1" s="1" t="s">
         <v>114</v>
       </c>
@@ -9664,7 +9673,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:10">
       <c r="B2" s="1" t="s">
         <v>89</v>
       </c>
@@ -9678,7 +9687,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:10">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -9692,7 +9701,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:10">
       <c r="B4" s="5"/>
       <c r="C4" s="43" t="s">
         <v>93</v>
@@ -9702,11 +9711,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:10">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -9714,15 +9723,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.1">
-      <c r="B6" s="111" t="s">
+    <row r="6" spans="2:10">
+      <c r="B6" s="110" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="111"/>
+      <c r="C6" s="110"/>
       <c r="D6" s="6"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:10">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -9736,7 +9745,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:10">
       <c r="B8" s="5" t="s">
         <v>96</v>
       </c>
@@ -9748,27 +9757,27 @@
       </c>
       <c r="E8" s="15"/>
     </row>
-    <row r="9" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:10" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-    </row>
-    <row r="10" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+    </row>
+    <row r="10" spans="2:10" ht="13.5" customHeight="1">
       <c r="B10" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="118" t="s">
+      <c r="C10" s="117" t="s">
         <v>99</v>
       </c>
-      <c r="D10" s="118"/>
-      <c r="E10" s="118"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.1">
+      <c r="D10" s="117"/>
+      <c r="E10" s="117"/>
+    </row>
+    <row r="11" spans="2:10">
       <c r="B11" s="50" t="s">
         <v>24</v>
       </c>
@@ -9776,22 +9785,22 @@
       <c r="D11" s="20"/>
       <c r="E11" s="21"/>
     </row>
-    <row r="12" spans="2:10" ht="96" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B12" s="119" t="s">
+    <row r="12" spans="2:10" ht="96" customHeight="1">
+      <c r="B12" s="118" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="119"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
-    </row>
-    <row r="13" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+    </row>
+    <row r="13" spans="2:10" ht="16.5" customHeight="1">
       <c r="B13" s="22"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="24"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="14" spans="2:10" ht="16.5" customHeight="1">
       <c r="B14" s="25" t="s">
         <v>25</v>
       </c>
@@ -9803,7 +9812,7 @@
       <c r="G14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="15" spans="2:10" ht="16.5" customHeight="1">
       <c r="B15" s="25" t="s">
         <v>26</v>
       </c>
@@ -9814,7 +9823,7 @@
       <c r="E15" s="52"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="16" spans="2:10" ht="16.5" customHeight="1">
       <c r="B16" s="25" t="s">
         <v>27</v>
       </c>
@@ -9825,14 +9834,14 @@
       <c r="E16" s="52"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="17" spans="2:11" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="51"/>
       <c r="D17" s="51"/>
       <c r="E17" s="52"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:11">
       <c r="B18" s="29" t="s">
         <v>28</v>
       </c>
@@ -9843,7 +9852,7 @@
       <c r="E18" s="55"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:11">
       <c r="B19" s="29"/>
       <c r="C19" s="54" t="s">
         <v>120</v>
@@ -9852,7 +9861,7 @@
       <c r="E19" s="55"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:11" ht="15.75">
       <c r="B20" s="29"/>
       <c r="C20" s="61" t="s">
         <v>121</v>
@@ -9862,7 +9871,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="58"/>
     </row>
-    <row r="21" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:11" ht="15.6" customHeight="1">
       <c r="B21" s="29"/>
       <c r="C21" s="72" t="s">
         <v>122</v>
@@ -9872,14 +9881,14 @@
       <c r="J21" s="1"/>
       <c r="K21" s="58"/>
     </row>
-    <row r="22" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:11" ht="15.6" customHeight="1">
       <c r="B22" s="29"/>
       <c r="D22" s="56"/>
       <c r="E22" s="57"/>
       <c r="J22" s="1"/>
       <c r="K22" s="58"/>
     </row>
-    <row r="23" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:11" ht="15" customHeight="1">
       <c r="B23" s="29"/>
       <c r="C23" s="54" t="s">
         <v>123</v>
@@ -9889,7 +9898,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="58"/>
     </row>
-    <row r="24" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:11" ht="15" customHeight="1">
       <c r="B24" s="29" t="s">
         <v>29</v>
       </c>
@@ -9901,7 +9910,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="58"/>
     </row>
-    <row r="25" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:11" ht="15" customHeight="1">
       <c r="B25" s="29"/>
       <c r="C25" s="53" t="s">
         <v>125</v>
@@ -9911,14 +9920,14 @@
       <c r="J25" s="1"/>
       <c r="K25" s="58"/>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:11" ht="15" customHeight="1">
       <c r="B26" s="29"/>
       <c r="D26" s="54"/>
       <c r="E26" s="55"/>
       <c r="J26" s="1"/>
       <c r="K26" s="58"/>
     </row>
-    <row r="27" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:11" ht="15.75">
       <c r="B27" s="29"/>
       <c r="C27" s="1" t="s">
         <v>126</v>
@@ -9928,13 +9937,13 @@
       <c r="J27" s="1"/>
       <c r="K27" s="58"/>
     </row>
-    <row r="28" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:11" ht="15" customHeight="1">
       <c r="B28" s="29"/>
       <c r="D28" s="73"/>
       <c r="E28" s="62"/>
       <c r="K28" s="58"/>
     </row>
-    <row r="29" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:11" ht="15" customHeight="1">
       <c r="B29" s="29"/>
       <c r="C29" s="63" t="s">
         <v>127</v>
@@ -9943,13 +9952,13 @@
       <c r="E29" s="62"/>
       <c r="K29" s="58"/>
     </row>
-    <row r="30" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:11" ht="15" customHeight="1">
       <c r="B30" s="29"/>
       <c r="D30" s="64"/>
       <c r="E30" s="62"/>
       <c r="K30" s="58"/>
     </row>
-    <row r="31" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:11" ht="15" customHeight="1">
       <c r="B31" s="29"/>
       <c r="C31" s="60" t="s">
         <v>128</v>
@@ -9958,7 +9967,7 @@
       <c r="E31" s="62"/>
       <c r="K31" s="58"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:11">
       <c r="B32" s="31"/>
       <c r="C32" s="54" t="s">
         <v>129</v>
@@ -9966,13 +9975,13 @@
       <c r="D32" s="61"/>
       <c r="E32" s="62"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:10">
       <c r="B33" s="31"/>
       <c r="C33" s="54"/>
       <c r="D33" s="61"/>
       <c r="E33" s="62"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:10">
       <c r="B34" s="29" t="s">
         <v>30</v>
       </c>
@@ -9982,13 +9991,13 @@
       <c r="D34" s="54"/>
       <c r="E34" s="55"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:10">
       <c r="B35" s="29"/>
       <c r="C35" s="56"/>
       <c r="D35" s="56"/>
       <c r="E35" s="57"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:10">
       <c r="B36" s="29" t="s">
         <v>31</v>
       </c>
@@ -9997,13 +10006,13 @@
       <c r="E36" s="57"/>
       <c r="J36" s="1"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:10">
       <c r="B37" s="29"/>
       <c r="C37" s="56"/>
       <c r="D37" s="56"/>
       <c r="E37" s="57"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:10">
       <c r="B38" s="29" t="s">
         <v>32</v>
       </c>
@@ -10011,19 +10020,19 @@
       <c r="D38" s="54"/>
       <c r="E38" s="55"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:10">
       <c r="B39" s="29"/>
       <c r="C39" s="54"/>
       <c r="D39" s="54"/>
       <c r="E39" s="55"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:10">
       <c r="B40" s="29"/>
       <c r="C40" s="54"/>
       <c r="D40" s="54"/>
       <c r="E40" s="55"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="41" spans="2:10">
       <c r="B41" s="32" t="s">
         <v>33</v>
       </c>
@@ -10033,7 +10042,7 @@
       <c r="D41" s="54"/>
       <c r="E41" s="55"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:10">
       <c r="B42" s="34"/>
       <c r="C42" s="56" t="s">
         <v>113</v>
@@ -10041,7 +10050,7 @@
       <c r="D42" s="54"/>
       <c r="E42" s="55"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:10">
       <c r="B43" s="34"/>
       <c r="C43" s="56" t="s">
         <v>35</v>
@@ -10049,21 +10058,21 @@
       <c r="D43" s="54"/>
       <c r="E43" s="55"/>
     </row>
-    <row r="44" spans="2:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:10" ht="15.6" customHeight="1">
       <c r="B44" s="34"/>
-      <c r="C44" s="116" t="s">
+      <c r="C44" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="D44" s="116"/>
-      <c r="E44" s="116"/>
-    </row>
-    <row r="45" spans="2:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D44" s="115"/>
+      <c r="E44" s="115"/>
+    </row>
+    <row r="45" spans="2:10" ht="15.6" customHeight="1">
       <c r="B45" s="31"/>
       <c r="C45" s="65"/>
       <c r="D45" s="66"/>
       <c r="E45" s="67"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:10">
       <c r="B46" s="31"/>
       <c r="C46" s="56" t="s">
         <v>36</v>
@@ -10071,7 +10080,7 @@
       <c r="D46" s="54"/>
       <c r="E46" s="55"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:10">
       <c r="B47" s="31"/>
       <c r="C47" s="54" t="s">
         <v>113</v>
@@ -10080,14 +10089,14 @@
       <c r="E47" s="55"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:10">
       <c r="B48" s="34"/>
       <c r="C48" s="56"/>
       <c r="D48" s="54"/>
       <c r="E48" s="55"/>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="49" spans="2:10">
       <c r="B49" s="34"/>
       <c r="C49" s="56"/>
       <c r="D49" s="54"/>
@@ -10095,35 +10104,35 @@
       <c r="G49" s="1"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="2:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="50" spans="2:10" ht="13.15" customHeight="1">
       <c r="B50" s="31"/>
       <c r="C50" s="56"/>
       <c r="D50" s="54"/>
       <c r="E50" s="55"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="51" spans="2:10">
       <c r="B51" s="31"/>
       <c r="C51" s="56"/>
       <c r="D51" s="54"/>
       <c r="E51" s="55"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="52" spans="2:10">
       <c r="B52" s="31"/>
       <c r="C52" s="56"/>
       <c r="D52" s="54"/>
       <c r="E52" s="55"/>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="53" spans="2:10">
       <c r="B53" s="31"/>
       <c r="C53" s="54"/>
       <c r="D53" s="54"/>
       <c r="E53" s="55"/>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="54" spans="2:10">
       <c r="B54" s="31"/>
       <c r="C54" s="54"/>
       <c r="D54" s="54"/>
@@ -10131,43 +10140,43 @@
       <c r="G54" s="1"/>
       <c r="J54" s="1"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="55" spans="2:10">
       <c r="B55" s="31"/>
       <c r="C55" s="54"/>
       <c r="D55" s="54"/>
       <c r="E55" s="55"/>
       <c r="J55" s="1"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="56" spans="2:10">
       <c r="B56" s="31"/>
       <c r="C56" s="54"/>
       <c r="D56" s="54"/>
       <c r="E56" s="55"/>
       <c r="J56" s="1"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="57" spans="2:10">
       <c r="B57" s="36"/>
       <c r="C57" s="68"/>
       <c r="D57" s="69"/>
       <c r="E57" s="70"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="58" spans="2:10">
       <c r="J58" s="1"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="59" spans="2:10">
       <c r="J59" s="1"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="60" spans="2:10">
       <c r="J60" s="1"/>
     </row>
-    <row r="61" spans="2:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="61" spans="2:10" ht="13.15" customHeight="1">
       <c r="G61" s="1"/>
       <c r="J61" s="1"/>
     </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.1">
+    <row r="76" spans="3:4">
       <c r="D76" s="1"/>
     </row>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.1">
+    <row r="77" spans="3:4">
       <c r="C77" s="33"/>
       <c r="D77" s="1"/>
     </row>
@@ -10180,6 +10189,7 @@
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -10198,18 +10208,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:K70"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="20.31640625" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:10">
       <c r="B1" s="1" t="s">
         <v>131</v>
       </c>
@@ -10217,7 +10227,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:10">
       <c r="B2" s="1" t="s">
         <v>89</v>
       </c>
@@ -10231,7 +10241,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:10">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -10245,7 +10255,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:10" ht="13.5" customHeight="1">
       <c r="B4" s="74" t="s">
         <v>134</v>
       </c>
@@ -10259,11 +10269,11 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:10">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -10271,11 +10281,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B6" s="120" t="s">
+    <row r="6" spans="2:10" ht="13.9" customHeight="1">
+      <c r="B6" s="119" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="120"/>
+      <c r="C6" s="119"/>
       <c r="D6" s="76" t="s">
         <v>139</v>
       </c>
@@ -10283,7 +10293,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:10">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -10297,7 +10307,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:10">
       <c r="B8" s="5" t="s">
         <v>141</v>
       </c>
@@ -10311,27 +10321,27 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:10" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-    </row>
-    <row r="10" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+    </row>
+    <row r="10" spans="2:10" ht="13.5" customHeight="1">
       <c r="B10" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="C10" s="121" t="s">
+      <c r="C10" s="120" t="s">
         <v>144</v>
       </c>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.1">
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+    </row>
+    <row r="11" spans="2:10">
       <c r="B11" s="50" t="s">
         <v>24</v>
       </c>
@@ -10339,22 +10349,22 @@
       <c r="D11" s="20"/>
       <c r="E11" s="21"/>
     </row>
-    <row r="12" spans="2:10" ht="96" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B12" s="122" t="s">
+    <row r="12" spans="2:10" ht="96" customHeight="1">
+      <c r="B12" s="121" t="s">
         <v>145</v>
       </c>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-    </row>
-    <row r="13" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="C12" s="121"/>
+      <c r="D12" s="121"/>
+      <c r="E12" s="121"/>
+    </row>
+    <row r="13" spans="2:10" ht="16.5" customHeight="1">
       <c r="B13" s="22"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="24"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="14" spans="2:10" ht="16.5" customHeight="1">
       <c r="B14" s="25" t="s">
         <v>25</v>
       </c>
@@ -10366,7 +10376,7 @@
       <c r="G14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="15" spans="2:10" ht="16.5" customHeight="1">
       <c r="B15" s="25" t="s">
         <v>26</v>
       </c>
@@ -10377,7 +10387,7 @@
       <c r="E15" s="52"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="16" spans="2:10" ht="16.5" customHeight="1">
       <c r="B16" s="25" t="s">
         <v>27</v>
       </c>
@@ -10388,14 +10398,14 @@
       <c r="E16" s="52"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="17" spans="2:11" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="51"/>
       <c r="D17" s="51"/>
       <c r="E17" s="52"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:11">
       <c r="B18" s="29" t="s">
         <v>28</v>
       </c>
@@ -10406,13 +10416,13 @@
       <c r="E18" s="55"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:11">
       <c r="B19" s="29"/>
       <c r="D19" s="54"/>
       <c r="E19" s="55"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:11" ht="15.75">
       <c r="B20" s="29"/>
       <c r="C20" t="s">
         <v>148</v>
@@ -10422,7 +10432,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="58"/>
     </row>
-    <row r="21" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:11" ht="15.6" customHeight="1">
       <c r="B21" s="29"/>
       <c r="C21" t="s">
         <v>149</v>
@@ -10432,7 +10442,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="58"/>
     </row>
-    <row r="22" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:11" ht="15.6" customHeight="1">
       <c r="B22" s="29"/>
       <c r="C22" s="81" t="s">
         <v>150</v>
@@ -10442,14 +10452,14 @@
       <c r="J22" s="1"/>
       <c r="K22" s="58"/>
     </row>
-    <row r="23" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:11" ht="15" customHeight="1">
       <c r="B23" s="29"/>
       <c r="D23" s="54"/>
       <c r="E23" s="55"/>
       <c r="J23" s="1"/>
       <c r="K23" s="58"/>
     </row>
-    <row r="24" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:11" ht="15.75">
       <c r="B24" s="29" t="s">
         <v>29</v>
       </c>
@@ -10461,19 +10471,19 @@
       <c r="J24" s="1"/>
       <c r="K24" s="58"/>
     </row>
-    <row r="25" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:11" ht="15" customHeight="1">
       <c r="B25" s="29"/>
       <c r="D25" s="73"/>
       <c r="E25" s="62"/>
       <c r="K25" s="58"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:11">
       <c r="B26" s="31"/>
       <c r="C26" s="54"/>
       <c r="D26" s="61"/>
       <c r="E26" s="62"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:11">
       <c r="B27" s="29" t="s">
         <v>30</v>
       </c>
@@ -10483,13 +10493,13 @@
       <c r="D27" s="54"/>
       <c r="E27" s="55"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:11">
       <c r="B28" s="29"/>
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
       <c r="E28" s="57"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:11">
       <c r="B29" s="29" t="s">
         <v>31</v>
       </c>
@@ -10500,13 +10510,13 @@
       <c r="E29" s="57"/>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:11">
       <c r="B30" s="29"/>
       <c r="C30" s="56"/>
       <c r="D30" s="56"/>
       <c r="E30" s="57"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:11">
       <c r="B31" s="29" t="s">
         <v>32</v>
       </c>
@@ -10516,19 +10526,19 @@
       <c r="D31" s="54"/>
       <c r="E31" s="55"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:11">
       <c r="B32" s="29"/>
       <c r="C32" s="54"/>
       <c r="D32" s="54"/>
       <c r="E32" s="55"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:10">
       <c r="B33" s="29"/>
       <c r="C33" s="54"/>
       <c r="D33" s="54"/>
       <c r="E33" s="55"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:10">
       <c r="B34" s="32" t="s">
         <v>33</v>
       </c>
@@ -10538,7 +10548,7 @@
       <c r="D34" s="54"/>
       <c r="E34" s="55"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:10">
       <c r="B35" s="34"/>
       <c r="C35" s="56" t="s">
         <v>113</v>
@@ -10546,7 +10556,7 @@
       <c r="D35" s="54"/>
       <c r="E35" s="55"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:10">
       <c r="B36" s="34"/>
       <c r="C36" s="56" t="s">
         <v>35</v>
@@ -10554,7 +10564,7 @@
       <c r="D36" s="54"/>
       <c r="E36" s="55"/>
     </row>
-    <row r="37" spans="2:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:10" ht="15.6" customHeight="1">
       <c r="B37" s="34"/>
       <c r="C37" s="65" t="s">
         <v>154</v>
@@ -10562,13 +10572,13 @@
       <c r="D37" s="66"/>
       <c r="E37" s="67"/>
     </row>
-    <row r="38" spans="2:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:10" ht="15.6" customHeight="1">
       <c r="B38" s="31"/>
       <c r="C38" s="65"/>
       <c r="D38" s="66"/>
       <c r="E38" s="67"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:10">
       <c r="B39" s="31"/>
       <c r="C39" s="56" t="s">
         <v>36</v>
@@ -10576,7 +10586,7 @@
       <c r="D39" s="54"/>
       <c r="E39" s="55"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:10">
       <c r="B40" s="31"/>
       <c r="C40" s="54" t="s">
         <v>155</v>
@@ -10585,14 +10595,14 @@
       <c r="E40" s="55"/>
       <c r="J40" s="1"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="41" spans="2:10">
       <c r="B41" s="34"/>
       <c r="C41" s="56"/>
       <c r="D41" s="54"/>
       <c r="E41" s="55"/>
       <c r="J41" s="1"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:10">
       <c r="B42" s="34"/>
       <c r="C42" s="56"/>
       <c r="D42" s="54"/>
@@ -10600,35 +10610,35 @@
       <c r="G42" s="1"/>
       <c r="J42" s="1"/>
     </row>
-    <row r="43" spans="2:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:10" ht="13.15" customHeight="1">
       <c r="B43" s="31"/>
       <c r="C43" s="56"/>
       <c r="D43" s="54"/>
       <c r="E43" s="55"/>
       <c r="J43" s="1"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:10">
       <c r="B44" s="31"/>
       <c r="C44" s="56"/>
       <c r="D44" s="54"/>
       <c r="E44" s="55"/>
       <c r="J44" s="1"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="45" spans="2:10">
       <c r="B45" s="31"/>
       <c r="C45" s="56"/>
       <c r="D45" s="54"/>
       <c r="E45" s="55"/>
       <c r="J45" s="1"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:10">
       <c r="B46" s="31"/>
       <c r="C46" s="54"/>
       <c r="D46" s="54"/>
       <c r="E46" s="55"/>
       <c r="J46" s="1"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:10">
       <c r="B47" s="31"/>
       <c r="C47" s="54"/>
       <c r="D47" s="54"/>
@@ -10636,43 +10646,43 @@
       <c r="G47" s="1"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:10">
       <c r="B48" s="31"/>
       <c r="C48" s="54"/>
       <c r="D48" s="54"/>
       <c r="E48" s="55"/>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="49" spans="2:10">
       <c r="B49" s="31"/>
       <c r="C49" s="54"/>
       <c r="D49" s="54"/>
       <c r="E49" s="55"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="50" spans="2:10">
       <c r="B50" s="36"/>
       <c r="C50" s="68"/>
       <c r="D50" s="69"/>
       <c r="E50" s="70"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="51" spans="2:10">
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="52" spans="2:10">
       <c r="J52" s="1"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="53" spans="2:10">
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="2:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="54" spans="2:10" ht="13.15" customHeight="1">
       <c r="G54" s="1"/>
       <c r="J54" s="1"/>
     </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.1">
+    <row r="69" spans="3:4">
       <c r="D69" s="1"/>
     </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.1">
+    <row r="70" spans="3:4">
       <c r="C70" s="33"/>
       <c r="D70" s="1"/>
     </row>
@@ -10684,6 +10694,7 @@
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -10702,18 +10713,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:K79"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="20.31640625" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:5">
       <c r="B1" s="1" t="s">
         <v>156</v>
       </c>
@@ -10721,7 +10732,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
         <v>89</v>
       </c>
@@ -10735,7 +10746,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:5">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -10749,7 +10760,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:5" ht="13.5" customHeight="1">
       <c r="B4" s="74" t="s">
         <v>134</v>
       </c>
@@ -10763,11 +10774,11 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:5">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -10775,11 +10786,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B6" s="120" t="s">
+    <row r="6" spans="2:5" ht="13.9" customHeight="1">
+      <c r="B6" s="119" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="120"/>
+      <c r="C6" s="119"/>
       <c r="D6" s="76" t="s">
         <v>139</v>
       </c>
@@ -10787,7 +10798,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:5">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -10801,7 +10812,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>141</v>
       </c>
@@ -10815,27 +10826,27 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:5" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-    </row>
-    <row r="10" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+    </row>
+    <row r="10" spans="2:5" ht="13.5" customHeight="1">
       <c r="B10" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="C10" s="121" t="s">
+      <c r="C10" s="120" t="s">
         <v>144</v>
       </c>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.1">
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" s="82" t="s">
         <v>24</v>
       </c>
@@ -10843,46 +10854,46 @@
       <c r="D11" s="84"/>
       <c r="E11" s="85"/>
     </row>
-    <row r="12" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B12" s="125" t="s">
+    <row r="12" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B12" s="124" t="s">
         <v>159</v>
       </c>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-    </row>
-    <row r="13" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B13" s="123"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
-    </row>
-    <row r="14" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B14" s="123"/>
-      <c r="C14" s="123"/>
-      <c r="D14" s="123"/>
-      <c r="E14" s="123"/>
-    </row>
-    <row r="15" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B15" s="123"/>
-      <c r="C15" s="123"/>
-      <c r="D15" s="123"/>
-      <c r="E15" s="123"/>
-    </row>
-    <row r="16" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B16" s="124"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="124"/>
-    </row>
-    <row r="17" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+    </row>
+    <row r="13" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+    </row>
+    <row r="14" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+    </row>
+    <row r="15" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+    </row>
+    <row r="16" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B16" s="123"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="123"/>
+    </row>
+    <row r="17" spans="2:11" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="27"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:11" ht="16.5" customHeight="1">
       <c r="B18" s="25" t="s">
         <v>25</v>
       </c>
@@ -10894,7 +10905,7 @@
       <c r="G18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:11" ht="16.5" customHeight="1">
       <c r="B19" s="25" t="s">
         <v>26</v>
       </c>
@@ -10905,7 +10916,7 @@
       <c r="E19" s="52"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:11" ht="16.5" customHeight="1">
       <c r="B20" s="25" t="s">
         <v>27</v>
       </c>
@@ -10916,14 +10927,14 @@
       <c r="E20" s="52"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:11" ht="16.5" customHeight="1">
       <c r="B21" s="28"/>
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
       <c r="E21" s="52"/>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:11">
       <c r="B22" s="29" t="s">
         <v>28</v>
       </c>
@@ -10934,14 +10945,14 @@
       <c r="E22" s="55"/>
       <c r="J22" s="1"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:11">
       <c r="B23" s="29"/>
       <c r="C23" s="81"/>
       <c r="D23" s="54"/>
       <c r="E23" s="55"/>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:11">
       <c r="B24" s="29"/>
       <c r="C24" s="81" t="s">
         <v>162</v>
@@ -10950,14 +10961,14 @@
       <c r="E24" s="55"/>
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:11">
       <c r="B25" s="29"/>
       <c r="C25" s="86"/>
       <c r="D25" s="54"/>
       <c r="E25" s="55"/>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:11" ht="15.6" customHeight="1">
       <c r="B26" s="29"/>
       <c r="C26" s="81" t="s">
         <v>163</v>
@@ -10967,7 +10978,7 @@
       <c r="J26" s="1"/>
       <c r="K26" s="58"/>
     </row>
-    <row r="27" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:11" ht="15.6" customHeight="1">
       <c r="B27" s="29"/>
       <c r="C27" s="81" t="s">
         <v>164</v>
@@ -10977,7 +10988,7 @@
       <c r="J27" s="1"/>
       <c r="K27" s="58"/>
     </row>
-    <row r="28" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:11" ht="15.6" customHeight="1">
       <c r="B28" s="29"/>
       <c r="C28" s="81"/>
       <c r="D28" s="54"/>
@@ -10985,7 +10996,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="58"/>
     </row>
-    <row r="29" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:11" ht="15.6" customHeight="1">
       <c r="B29" s="29"/>
       <c r="C29" s="81" t="s">
         <v>165</v>
@@ -10997,7 +11008,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="58"/>
     </row>
-    <row r="30" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:11" ht="15.6" customHeight="1">
       <c r="B30" s="29"/>
       <c r="C30" s="81" t="s">
         <v>167</v>
@@ -11009,7 +11020,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="58"/>
     </row>
-    <row r="31" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:11" ht="15.6" customHeight="1">
       <c r="B31" s="29"/>
       <c r="C31" s="81" t="s">
         <v>169</v>
@@ -11021,14 +11032,14 @@
       <c r="J31" s="1"/>
       <c r="K31" s="58"/>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:11" ht="15" customHeight="1">
       <c r="B32" s="29"/>
       <c r="D32" s="54"/>
       <c r="E32" s="55"/>
       <c r="J32" s="1"/>
       <c r="K32" s="58"/>
     </row>
-    <row r="33" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:11" ht="15.75">
       <c r="B33" s="29" t="s">
         <v>29</v>
       </c>
@@ -11040,7 +11051,7 @@
       <c r="J33" s="1"/>
       <c r="K33" s="58"/>
     </row>
-    <row r="34" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:11" ht="15" customHeight="1">
       <c r="B34" s="29"/>
       <c r="C34" t="s">
         <v>172</v>
@@ -11049,13 +11060,13 @@
       <c r="E34" s="62"/>
       <c r="K34" s="58"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:11">
       <c r="B35" s="31"/>
       <c r="C35" s="54"/>
       <c r="D35" s="61"/>
       <c r="E35" s="62"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:11">
       <c r="B36" s="29" t="s">
         <v>30</v>
       </c>
@@ -11065,13 +11076,13 @@
       <c r="D36" s="54"/>
       <c r="E36" s="55"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:11">
       <c r="B37" s="29"/>
       <c r="C37" s="56"/>
       <c r="D37" s="56"/>
       <c r="E37" s="57"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:11">
       <c r="B38" s="29" t="s">
         <v>31</v>
       </c>
@@ -11080,13 +11091,13 @@
       <c r="E38" s="57"/>
       <c r="J38" s="1"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:11">
       <c r="B39" s="29"/>
       <c r="C39" s="56"/>
       <c r="D39" s="56"/>
       <c r="E39" s="57"/>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:11">
       <c r="B40" s="29" t="s">
         <v>32</v>
       </c>
@@ -11096,7 +11107,7 @@
       <c r="D40" s="54"/>
       <c r="E40" s="55"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="41" spans="2:11">
       <c r="B41" s="29"/>
       <c r="C41" s="54" t="s">
         <v>173</v>
@@ -11104,13 +11115,13 @@
       <c r="D41" s="54"/>
       <c r="E41" s="55"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:11">
       <c r="B42" s="29"/>
       <c r="C42" s="54"/>
       <c r="D42" s="54"/>
       <c r="E42" s="55"/>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:11">
       <c r="B43" s="32" t="s">
         <v>33</v>
       </c>
@@ -11120,7 +11131,7 @@
       <c r="D43" s="54"/>
       <c r="E43" s="55"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:11">
       <c r="B44" s="34"/>
       <c r="C44" s="54" t="s">
         <v>155</v>
@@ -11128,7 +11139,7 @@
       <c r="D44" s="54"/>
       <c r="E44" s="55"/>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="45" spans="2:11">
       <c r="B45" s="34"/>
       <c r="C45" s="56" t="s">
         <v>35</v>
@@ -11136,7 +11147,7 @@
       <c r="D45" s="54"/>
       <c r="E45" s="55"/>
     </row>
-    <row r="46" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:11" ht="15.6" customHeight="1">
       <c r="B46" s="34"/>
       <c r="C46" s="56" t="s">
         <v>174</v>
@@ -11144,13 +11155,13 @@
       <c r="D46" s="66"/>
       <c r="E46" s="67"/>
     </row>
-    <row r="47" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:11" ht="15.6" customHeight="1">
       <c r="B47" s="31"/>
       <c r="C47" s="65"/>
       <c r="D47" s="66"/>
       <c r="E47" s="67"/>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:11">
       <c r="B48" s="31"/>
       <c r="C48" s="56" t="s">
         <v>36</v>
@@ -11158,21 +11169,21 @@
       <c r="D48" s="54"/>
       <c r="E48" s="55"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="49" spans="2:10">
       <c r="B49" s="31"/>
       <c r="C49" s="54"/>
       <c r="D49" s="54"/>
       <c r="E49" s="55"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="50" spans="2:10">
       <c r="B50" s="34"/>
       <c r="C50" s="56"/>
       <c r="D50" s="54"/>
       <c r="E50" s="55"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="51" spans="2:10">
       <c r="B51" s="34"/>
       <c r="C51" s="56"/>
       <c r="D51" s="54"/>
@@ -11180,35 +11191,35 @@
       <c r="G51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="2:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="52" spans="2:10" ht="13.15" customHeight="1">
       <c r="B52" s="31"/>
       <c r="C52" s="56"/>
       <c r="D52" s="54"/>
       <c r="E52" s="55"/>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="53" spans="2:10">
       <c r="B53" s="31"/>
       <c r="C53" s="56"/>
       <c r="D53" s="54"/>
       <c r="E53" s="55"/>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="54" spans="2:10">
       <c r="B54" s="31"/>
       <c r="C54" s="56"/>
       <c r="D54" s="54"/>
       <c r="E54" s="55"/>
       <c r="J54" s="1"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="55" spans="2:10">
       <c r="B55" s="31"/>
       <c r="C55" s="54"/>
       <c r="D55" s="54"/>
       <c r="E55" s="55"/>
       <c r="J55" s="1"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="56" spans="2:10">
       <c r="B56" s="31"/>
       <c r="C56" s="54"/>
       <c r="D56" s="54"/>
@@ -11216,43 +11227,43 @@
       <c r="G56" s="1"/>
       <c r="J56" s="1"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="57" spans="2:10">
       <c r="B57" s="31"/>
       <c r="C57" s="54"/>
       <c r="D57" s="54"/>
       <c r="E57" s="55"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="58" spans="2:10">
       <c r="B58" s="31"/>
       <c r="C58" s="54"/>
       <c r="D58" s="54"/>
       <c r="E58" s="55"/>
       <c r="J58" s="1"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="59" spans="2:10">
       <c r="B59" s="36"/>
       <c r="C59" s="68"/>
       <c r="D59" s="69"/>
       <c r="E59" s="70"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="60" spans="2:10">
       <c r="J60" s="1"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="61" spans="2:10">
       <c r="J61" s="1"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="62" spans="2:10">
       <c r="J62" s="1"/>
     </row>
-    <row r="63" spans="2:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="63" spans="2:10" ht="13.15" customHeight="1">
       <c r="G63" s="1"/>
       <c r="J63" s="1"/>
     </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.1">
+    <row r="78" spans="3:4">
       <c r="D78" s="1"/>
     </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.1">
+    <row r="79" spans="3:4">
       <c r="C79" s="33"/>
       <c r="D79" s="1"/>
     </row>
@@ -11268,6 +11279,7 @@
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -11290,18 +11302,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B1:K79"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="21.1328125" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="21.125" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:5">
       <c r="B1" s="1" t="s">
         <v>156</v>
       </c>
@@ -11309,7 +11321,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
         <v>89</v>
       </c>
@@ -11323,7 +11335,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:5">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -11337,7 +11349,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:5" ht="13.5" customHeight="1">
       <c r="B4" s="74" t="s">
         <v>134</v>
       </c>
@@ -11351,11 +11363,11 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:5">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -11363,11 +11375,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B6" s="120" t="s">
+    <row r="6" spans="2:5" ht="13.9" customHeight="1">
+      <c r="B6" s="119" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="120"/>
+      <c r="C6" s="119"/>
       <c r="D6" s="76" t="s">
         <v>139</v>
       </c>
@@ -11375,7 +11387,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:5">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -11389,7 +11401,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>141</v>
       </c>
@@ -11403,27 +11415,27 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:5" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-    </row>
-    <row r="10" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+    </row>
+    <row r="10" spans="2:5" ht="13.5" customHeight="1">
       <c r="B10" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="C10" s="121" t="s">
+      <c r="C10" s="120" t="s">
         <v>144</v>
       </c>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.1">
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" s="82" t="s">
         <v>24</v>
       </c>
@@ -11431,46 +11443,46 @@
       <c r="D11" s="84"/>
       <c r="E11" s="85"/>
     </row>
-    <row r="12" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B12" s="125" t="s">
+    <row r="12" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B12" s="124" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-    </row>
-    <row r="13" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B13" s="123"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
-    </row>
-    <row r="14" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B14" s="123"/>
-      <c r="C14" s="123"/>
-      <c r="D14" s="123"/>
-      <c r="E14" s="123"/>
-    </row>
-    <row r="15" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B15" s="123"/>
-      <c r="C15" s="123"/>
-      <c r="D15" s="123"/>
-      <c r="E15" s="123"/>
-    </row>
-    <row r="16" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B16" s="124"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="124"/>
-    </row>
-    <row r="17" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+    </row>
+    <row r="13" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+    </row>
+    <row r="14" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+    </row>
+    <row r="15" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+    </row>
+    <row r="16" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B16" s="123"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="123"/>
+    </row>
+    <row r="17" spans="2:11" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="27"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:11" ht="16.5" customHeight="1">
       <c r="B18" s="25" t="s">
         <v>25</v>
       </c>
@@ -11482,7 +11494,7 @@
       <c r="G18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:11" ht="16.5" customHeight="1">
       <c r="B19" s="25" t="s">
         <v>26</v>
       </c>
@@ -11493,7 +11505,7 @@
       <c r="E19" s="52"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:11" ht="16.5" customHeight="1">
       <c r="B20" s="25" t="s">
         <v>27</v>
       </c>
@@ -11504,14 +11516,14 @@
       <c r="E20" s="52"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:11" ht="16.5" customHeight="1">
       <c r="B21" s="28"/>
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
       <c r="E21" s="52"/>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:11">
       <c r="B22" s="29" t="s">
         <v>28</v>
       </c>
@@ -11522,14 +11534,14 @@
       <c r="E22" s="55"/>
       <c r="J22" s="1"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:11">
       <c r="B23" s="29"/>
       <c r="C23" s="81"/>
       <c r="D23" s="54"/>
       <c r="E23" s="55"/>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:11">
       <c r="B24" s="29"/>
       <c r="C24" s="81" t="s">
         <v>164</v>
@@ -11540,14 +11552,14 @@
       </c>
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:11">
       <c r="B25" s="29"/>
       <c r="C25" s="86"/>
       <c r="D25" s="54"/>
       <c r="E25" s="55"/>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:11" ht="15.6" customHeight="1">
       <c r="B26" s="29"/>
       <c r="C26" s="81"/>
       <c r="D26" s="54"/>
@@ -11555,14 +11567,14 @@
       <c r="J26" s="1"/>
       <c r="K26" s="58"/>
     </row>
-    <row r="27" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:11" ht="15.6" customHeight="1">
       <c r="B27" s="29"/>
       <c r="D27" s="54"/>
       <c r="E27" s="57"/>
       <c r="J27" s="1"/>
       <c r="K27" s="58"/>
     </row>
-    <row r="28" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:11" ht="15.6" customHeight="1">
       <c r="B28" s="29"/>
       <c r="C28" s="81" t="s">
         <v>180</v>
@@ -11572,7 +11584,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="58"/>
     </row>
-    <row r="29" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:11" ht="15.6" customHeight="1">
       <c r="B29" s="29"/>
       <c r="C29" t="s">
         <v>181</v>
@@ -11584,7 +11596,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="58"/>
     </row>
-    <row r="30" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:11" ht="15.6" customHeight="1">
       <c r="B30" s="29"/>
       <c r="C30" s="81" t="s">
         <v>165</v>
@@ -11596,7 +11608,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="58"/>
     </row>
-    <row r="31" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:11" ht="15.6" customHeight="1">
       <c r="B31" s="29"/>
       <c r="C31" s="81" t="s">
         <v>167</v>
@@ -11608,7 +11620,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="58"/>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:11" ht="15" customHeight="1">
       <c r="B32" s="29"/>
       <c r="C32" s="81" t="s">
         <v>185</v>
@@ -11620,14 +11632,14 @@
       <c r="J32" s="1"/>
       <c r="K32" s="58"/>
     </row>
-    <row r="33" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:11" ht="15.75">
       <c r="B33" s="29"/>
       <c r="D33" s="61"/>
       <c r="E33" s="62"/>
       <c r="J33" s="1"/>
       <c r="K33" s="58"/>
     </row>
-    <row r="34" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:11" ht="15" customHeight="1">
       <c r="B34" s="29" t="s">
         <v>29</v>
       </c>
@@ -11638,7 +11650,7 @@
       <c r="E34" s="62"/>
       <c r="K34" s="58"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:11">
       <c r="B35" s="31"/>
       <c r="C35" s="54" t="s">
         <v>188</v>
@@ -11646,7 +11658,7 @@
       <c r="D35" s="61"/>
       <c r="E35" s="62"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:11">
       <c r="B36" s="31"/>
       <c r="C36" t="s">
         <v>189</v>
@@ -11654,12 +11666,12 @@
       <c r="D36" s="54"/>
       <c r="E36" s="55"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:11">
       <c r="B37" s="31"/>
       <c r="D37" s="56"/>
       <c r="E37" s="57"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:11">
       <c r="B38" s="29" t="s">
         <v>30</v>
       </c>
@@ -11670,13 +11682,13 @@
       <c r="E38" s="57"/>
       <c r="J38" s="1"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:11">
       <c r="B39" s="29"/>
       <c r="C39" s="54"/>
       <c r="D39" s="56"/>
       <c r="E39" s="57"/>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:11">
       <c r="B40" s="29" t="s">
         <v>31</v>
       </c>
@@ -11686,13 +11698,13 @@
       <c r="D40" s="54"/>
       <c r="E40" s="55"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="41" spans="2:11">
       <c r="B41" s="29"/>
       <c r="C41" s="54"/>
       <c r="D41" s="54"/>
       <c r="E41" s="55"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:11">
       <c r="B42" s="29" t="s">
         <v>32</v>
       </c>
@@ -11702,19 +11714,19 @@
       <c r="D42" s="54"/>
       <c r="E42" s="55"/>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:11">
       <c r="B43" s="29"/>
       <c r="C43" s="54"/>
       <c r="D43" s="54"/>
       <c r="E43" s="55"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:11">
       <c r="B44" s="29"/>
       <c r="C44" s="54"/>
       <c r="D44" s="54"/>
       <c r="E44" s="55"/>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="45" spans="2:11">
       <c r="B45" s="32" t="s">
         <v>33</v>
       </c>
@@ -11724,7 +11736,7 @@
       <c r="D45" s="54"/>
       <c r="E45" s="55"/>
     </row>
-    <row r="46" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:11" ht="15.6" customHeight="1">
       <c r="B46" s="34"/>
       <c r="C46" s="54" t="s">
         <v>190</v>
@@ -11732,7 +11744,7 @@
       <c r="D46" s="66"/>
       <c r="E46" s="67"/>
     </row>
-    <row r="47" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:11" ht="15.6" customHeight="1">
       <c r="B47" s="34"/>
       <c r="C47" s="56" t="s">
         <v>35</v>
@@ -11740,7 +11752,7 @@
       <c r="D47" s="66"/>
       <c r="E47" s="67"/>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:11">
       <c r="B48" s="34"/>
       <c r="C48" s="56" t="s">
         <v>191</v>
@@ -11748,14 +11760,14 @@
       <c r="D48" s="54"/>
       <c r="E48" s="55"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="49" spans="2:10">
       <c r="B49" s="31"/>
       <c r="C49" s="65"/>
       <c r="D49" s="54"/>
       <c r="E49" s="55"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="50" spans="2:10">
       <c r="B50" s="31"/>
       <c r="C50" s="56" t="s">
         <v>36</v>
@@ -11764,7 +11776,7 @@
       <c r="E50" s="55"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="51" spans="2:10">
       <c r="B51" s="34"/>
       <c r="C51" s="56" t="s">
         <v>192</v>
@@ -11774,35 +11786,35 @@
       <c r="G51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="2:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="52" spans="2:10" ht="13.15" customHeight="1">
       <c r="B52" s="31"/>
       <c r="C52" s="56"/>
       <c r="D52" s="54"/>
       <c r="E52" s="55"/>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="53" spans="2:10">
       <c r="B53" s="31"/>
       <c r="C53" s="56"/>
       <c r="D53" s="54"/>
       <c r="E53" s="55"/>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="54" spans="2:10">
       <c r="B54" s="31"/>
       <c r="C54" s="56"/>
       <c r="D54" s="54"/>
       <c r="E54" s="55"/>
       <c r="J54" s="1"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="55" spans="2:10">
       <c r="B55" s="31"/>
       <c r="C55" s="54"/>
       <c r="D55" s="54"/>
       <c r="E55" s="55"/>
       <c r="J55" s="1"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="56" spans="2:10">
       <c r="B56" s="31"/>
       <c r="C56" s="54"/>
       <c r="D56" s="54"/>
@@ -11810,43 +11822,43 @@
       <c r="G56" s="1"/>
       <c r="J56" s="1"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="57" spans="2:10">
       <c r="B57" s="31"/>
       <c r="C57" s="54"/>
       <c r="D57" s="54"/>
       <c r="E57" s="55"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="58" spans="2:10">
       <c r="B58" s="31"/>
       <c r="C58" s="54"/>
       <c r="D58" s="54"/>
       <c r="E58" s="55"/>
       <c r="J58" s="1"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="59" spans="2:10">
       <c r="B59" s="36"/>
       <c r="C59" s="68"/>
       <c r="D59" s="69"/>
       <c r="E59" s="70"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="60" spans="2:10">
       <c r="J60" s="1"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="61" spans="2:10">
       <c r="J61" s="1"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="62" spans="2:10">
       <c r="J62" s="1"/>
     </row>
-    <row r="63" spans="2:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="63" spans="2:10" ht="13.15" customHeight="1">
       <c r="G63" s="1"/>
       <c r="J63" s="1"/>
     </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.1">
+    <row r="78" spans="3:4">
       <c r="D78" s="1"/>
     </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.1">
+    <row r="79" spans="3:4">
       <c r="C79" s="33"/>
       <c r="D79" s="1"/>
     </row>
@@ -11862,6 +11874,7 @@
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -11880,18 +11893,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B1:K88"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.76953125" customWidth="1"/>
-    <col min="2" max="2" width="16.2265625" customWidth="1"/>
-    <col min="3" max="3" width="22.90625" customWidth="1"/>
-    <col min="4" max="4" width="25.76953125" customWidth="1"/>
-    <col min="5" max="5" width="32.04296875" customWidth="1"/>
-    <col min="6" max="6" width="1.2265625" customWidth="1"/>
-    <col min="7" max="1025" width="8.99609375" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="22.875" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="1.25" customWidth="1"/>
+    <col min="7" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="1" spans="2:5">
       <c r="B1" s="1" t="s">
         <v>156</v>
       </c>
@@ -11899,7 +11912,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
         <v>89</v>
       </c>
@@ -11913,7 +11926,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="3" spans="2:5">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -11927,7 +11940,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="4" spans="2:5" ht="13.5" customHeight="1">
       <c r="B4" s="74" t="s">
         <v>134</v>
       </c>
@@ -11941,11 +11954,11 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.1">
-      <c r="B5" s="110" t="s">
+    <row r="5" spans="2:5">
+      <c r="B5" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
@@ -11953,11 +11966,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B6" s="120" t="s">
+    <row r="6" spans="2:5" ht="13.9" customHeight="1">
+      <c r="B6" s="119" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="120"/>
+      <c r="C6" s="119"/>
       <c r="D6" s="76" t="s">
         <v>139</v>
       </c>
@@ -11965,7 +11978,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="7" spans="2:5">
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -11979,7 +11992,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.1">
+    <row r="8" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>141</v>
       </c>
@@ -11993,27 +12006,27 @@
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="2:5" ht="13.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-    </row>
-    <row r="10" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+    </row>
+    <row r="10" spans="2:5" ht="13.5" customHeight="1">
       <c r="B10" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="C10" s="121" t="s">
+      <c r="C10" s="120" t="s">
         <v>144</v>
       </c>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.1">
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" s="82" t="s">
         <v>24</v>
       </c>
@@ -12021,48 +12034,48 @@
       <c r="D11" s="84"/>
       <c r="E11" s="85"/>
     </row>
-    <row r="12" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B12" s="125" t="s">
+    <row r="12" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B12" s="124" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-    </row>
-    <row r="13" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B13" s="123" t="s">
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+    </row>
+    <row r="13" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B13" s="122" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
-    </row>
-    <row r="14" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B14" s="123"/>
-      <c r="C14" s="123"/>
-      <c r="D14" s="123"/>
-      <c r="E14" s="123"/>
-    </row>
-    <row r="15" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B15" s="123"/>
-      <c r="C15" s="123"/>
-      <c r="D15" s="123"/>
-      <c r="E15" s="123"/>
-    </row>
-    <row r="16" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="B16" s="124"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="124"/>
-    </row>
-    <row r="17" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+    </row>
+    <row r="14" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+    </row>
+    <row r="15" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+    </row>
+    <row r="16" spans="2:5" ht="19.5" customHeight="1">
+      <c r="B16" s="123"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="123"/>
+    </row>
+    <row r="17" spans="2:11" ht="16.5" customHeight="1">
       <c r="B17" s="28"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="27"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="18" spans="2:11" ht="16.5" customHeight="1">
       <c r="B18" s="25" t="s">
         <v>25</v>
       </c>
@@ -12074,7 +12087,7 @@
       <c r="G18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="19" spans="2:11" ht="16.5" customHeight="1">
       <c r="B19" s="25" t="s">
         <v>26</v>
       </c>
@@ -12085,7 +12098,7 @@
       <c r="E19" s="52"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="20" spans="2:11" ht="16.5" customHeight="1">
       <c r="B20" s="25" t="s">
         <v>27</v>
       </c>
@@ -12096,14 +12109,14 @@
       <c r="E20" s="52"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="21" spans="2:11" ht="16.5" customHeight="1">
       <c r="B21" s="28"/>
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
       <c r="E21" s="52"/>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="22" spans="2:11">
       <c r="B22" s="29" t="s">
         <v>28</v>
       </c>
@@ -12114,7 +12127,7 @@
       <c r="E22" s="55"/>
       <c r="J22" s="1"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="23" spans="2:11">
       <c r="B23" s="29"/>
       <c r="C23" s="88" t="s">
         <v>164</v>
@@ -12125,14 +12138,14 @@
       </c>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="24" spans="2:11" ht="15.6" customHeight="1">
       <c r="B24" s="29"/>
       <c r="D24" s="54"/>
       <c r="E24" s="57"/>
       <c r="J24" s="1"/>
       <c r="K24" s="58"/>
     </row>
-    <row r="25" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="25" spans="2:11" ht="15.6" customHeight="1">
       <c r="B25" s="29"/>
       <c r="C25" s="89" t="s">
         <v>180</v>
@@ -12142,7 +12155,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="58"/>
     </row>
-    <row r="26" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="26" spans="2:11" ht="15.6" customHeight="1">
       <c r="B26" s="29"/>
       <c r="C26" s="90" t="s">
         <v>181</v>
@@ -12154,7 +12167,7 @@
       <c r="J26" s="1"/>
       <c r="K26" s="58"/>
     </row>
-    <row r="27" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="27" spans="2:11" ht="15.6" customHeight="1">
       <c r="B27" s="29"/>
       <c r="C27" s="88" t="s">
         <v>165</v>
@@ -12166,7 +12179,7 @@
       <c r="J27" s="1"/>
       <c r="K27" s="58"/>
     </row>
-    <row r="28" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="28" spans="2:11" ht="15.6" customHeight="1">
       <c r="B28" s="29"/>
       <c r="C28" s="88" t="s">
         <v>167</v>
@@ -12178,7 +12191,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="58"/>
     </row>
-    <row r="29" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="29" spans="2:11" ht="15" customHeight="1">
       <c r="B29" s="29"/>
       <c r="C29" s="88" t="s">
         <v>200</v>
@@ -12190,7 +12203,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="58"/>
     </row>
-    <row r="30" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="30" spans="2:11" ht="15.75">
       <c r="B30" s="29"/>
       <c r="C30" t="s">
         <v>202</v>
@@ -12202,7 +12215,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="58"/>
     </row>
-    <row r="31" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="31" spans="2:11" ht="15.75">
       <c r="B31" s="29"/>
       <c r="C31" t="s">
         <v>204</v>
@@ -12214,21 +12227,21 @@
       <c r="J31" s="1"/>
       <c r="K31" s="58"/>
     </row>
-    <row r="32" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="32" spans="2:11" ht="15.75">
       <c r="B32" s="29"/>
       <c r="D32" s="54"/>
       <c r="E32" s="62"/>
       <c r="J32" s="1"/>
       <c r="K32" s="58"/>
     </row>
-    <row r="33" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="33" spans="2:11" ht="15.75">
       <c r="B33" s="29"/>
       <c r="D33" s="61"/>
       <c r="E33" s="62"/>
       <c r="J33" s="1"/>
       <c r="K33" s="58"/>
     </row>
-    <row r="34" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="34" spans="2:11" ht="15.75">
       <c r="B34" s="29"/>
       <c r="C34" s="1" t="s">
         <v>206</v>
@@ -12238,7 +12251,7 @@
       <c r="J34" s="1"/>
       <c r="K34" s="58"/>
     </row>
-    <row r="35" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="35" spans="2:11" ht="15.75">
       <c r="B35" s="29"/>
       <c r="C35" t="s">
         <v>181</v>
@@ -12250,7 +12263,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="58"/>
     </row>
-    <row r="36" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="36" spans="2:11" ht="15.75">
       <c r="B36" s="29"/>
       <c r="C36" s="81" t="s">
         <v>165</v>
@@ -12262,7 +12275,7 @@
       <c r="J36" s="1"/>
       <c r="K36" s="58"/>
     </row>
-    <row r="37" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="37" spans="2:11" ht="15.75">
       <c r="B37" s="29"/>
       <c r="C37" s="81" t="s">
         <v>167</v>
@@ -12274,7 +12287,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="58"/>
     </row>
-    <row r="38" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="38" spans="2:11" ht="15.75">
       <c r="B38" s="29"/>
       <c r="C38" s="81" t="s">
         <v>200</v>
@@ -12286,7 +12299,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="58"/>
     </row>
-    <row r="39" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="39" spans="2:11" ht="15.75">
       <c r="B39" s="29"/>
       <c r="C39" t="s">
         <v>202</v>
@@ -12298,7 +12311,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="58"/>
     </row>
-    <row r="40" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="40" spans="2:11" ht="15.75">
       <c r="B40" s="29"/>
       <c r="C40" t="s">
         <v>204</v>
@@ -12310,21 +12323,21 @@
       <c r="J40" s="1"/>
       <c r="K40" s="58"/>
     </row>
-    <row r="41" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="41" spans="2:11" ht="15.75">
       <c r="B41" s="29"/>
       <c r="D41" s="54"/>
       <c r="E41" s="62"/>
       <c r="J41" s="1"/>
       <c r="K41" s="58"/>
     </row>
-    <row r="42" spans="2:11" ht="15.75" x14ac:dyDescent="0.1">
+    <row r="42" spans="2:11" ht="15.75">
       <c r="B42" s="29"/>
       <c r="D42" s="54"/>
       <c r="E42" s="62"/>
       <c r="J42" s="1"/>
       <c r="K42" s="58"/>
     </row>
-    <row r="43" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="43" spans="2:11" ht="15" customHeight="1">
       <c r="B43" s="29" t="s">
         <v>29</v>
       </c>
@@ -12334,20 +12347,20 @@
       <c r="E43" s="62"/>
       <c r="K43" s="58"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="44" spans="2:11">
       <c r="B44" s="31"/>
       <c r="E44" s="62"/>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="45" spans="2:11">
       <c r="B45" s="31"/>
       <c r="E45" s="55"/>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="46" spans="2:11">
       <c r="B46" s="31"/>
       <c r="D46" s="56"/>
       <c r="E46" s="57"/>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="47" spans="2:11">
       <c r="B47" s="29" t="s">
         <v>30</v>
       </c>
@@ -12358,13 +12371,13 @@
       <c r="E47" s="57"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.1">
+    <row r="48" spans="2:11">
       <c r="B48" s="29"/>
       <c r="C48" s="54"/>
       <c r="D48" s="56"/>
       <c r="E48" s="57"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="49" spans="2:10">
       <c r="B49" s="29" t="s">
         <v>31</v>
       </c>
@@ -12374,13 +12387,13 @@
       <c r="D49" s="54"/>
       <c r="E49" s="55"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="50" spans="2:10">
       <c r="B50" s="29"/>
       <c r="C50" s="54"/>
       <c r="D50" s="54"/>
       <c r="E50" s="55"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="51" spans="2:10">
       <c r="B51" s="29" t="s">
         <v>32</v>
       </c>
@@ -12390,19 +12403,19 @@
       <c r="D51" s="54"/>
       <c r="E51" s="55"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="52" spans="2:10">
       <c r="B52" s="29"/>
       <c r="C52" s="54"/>
       <c r="D52" s="54"/>
       <c r="E52" s="55"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="53" spans="2:10">
       <c r="B53" s="29"/>
       <c r="C53" s="54"/>
       <c r="D53" s="54"/>
       <c r="E53" s="55"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="54" spans="2:10">
       <c r="B54" s="32" t="s">
         <v>33</v>
       </c>
@@ -12412,7 +12425,7 @@
       <c r="D54" s="54"/>
       <c r="E54" s="55"/>
     </row>
-    <row r="55" spans="2:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="55" spans="2:10" ht="15.6" customHeight="1">
       <c r="B55" s="34"/>
       <c r="C55" s="54" t="s">
         <v>190</v>
@@ -12420,7 +12433,7 @@
       <c r="D55" s="66"/>
       <c r="E55" s="67"/>
     </row>
-    <row r="56" spans="2:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="56" spans="2:10" ht="15.6" customHeight="1">
       <c r="B56" s="34"/>
       <c r="C56" s="56" t="s">
         <v>35</v>
@@ -12428,7 +12441,7 @@
       <c r="D56" s="66"/>
       <c r="E56" s="67"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="57" spans="2:10">
       <c r="B57" s="34"/>
       <c r="C57" t="s">
         <v>215</v>
@@ -12436,14 +12449,14 @@
       <c r="D57" s="54"/>
       <c r="E57" s="55"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="58" spans="2:10">
       <c r="B58" s="31"/>
       <c r="C58" s="65"/>
       <c r="D58" s="54"/>
       <c r="E58" s="55"/>
       <c r="J58" s="1"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="59" spans="2:10">
       <c r="B59" s="31"/>
       <c r="C59" s="56" t="s">
         <v>36</v>
@@ -12452,7 +12465,7 @@
       <c r="E59" s="55"/>
       <c r="J59" s="1"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="60" spans="2:10">
       <c r="B60" s="34"/>
       <c r="C60" t="s">
         <v>216</v>
@@ -12462,35 +12475,35 @@
       <c r="G60" s="1"/>
       <c r="J60" s="1"/>
     </row>
-    <row r="61" spans="2:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="61" spans="2:10" ht="13.15" customHeight="1">
       <c r="B61" s="31"/>
       <c r="C61" s="56"/>
       <c r="D61" s="54"/>
       <c r="E61" s="55"/>
       <c r="J61" s="1"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="62" spans="2:10">
       <c r="B62" s="31"/>
       <c r="C62" s="56"/>
       <c r="D62" s="54"/>
       <c r="E62" s="55"/>
       <c r="J62" s="1"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="63" spans="2:10">
       <c r="B63" s="31"/>
       <c r="C63" s="56"/>
       <c r="D63" s="54"/>
       <c r="E63" s="55"/>
       <c r="J63" s="1"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="64" spans="2:10">
       <c r="B64" s="31"/>
       <c r="C64" s="54"/>
       <c r="D64" s="54"/>
       <c r="E64" s="55"/>
       <c r="J64" s="1"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="65" spans="2:10">
       <c r="B65" s="31"/>
       <c r="C65" s="54"/>
       <c r="D65" s="54"/>
@@ -12498,43 +12511,43 @@
       <c r="G65" s="1"/>
       <c r="J65" s="1"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="66" spans="2:10">
       <c r="B66" s="31"/>
       <c r="C66" s="54"/>
       <c r="D66" s="54"/>
       <c r="E66" s="55"/>
       <c r="J66" s="1"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="67" spans="2:10">
       <c r="B67" s="31"/>
       <c r="C67" s="54"/>
       <c r="D67" s="54"/>
       <c r="E67" s="55"/>
       <c r="J67" s="1"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="68" spans="2:10">
       <c r="B68" s="36"/>
       <c r="C68" s="68"/>
       <c r="D68" s="69"/>
       <c r="E68" s="70"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="69" spans="2:10">
       <c r="J69" s="1"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="70" spans="2:10">
       <c r="J70" s="1"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.1">
+    <row r="71" spans="2:10">
       <c r="J71" s="1"/>
     </row>
-    <row r="72" spans="2:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="72" spans="2:10" ht="13.15" customHeight="1">
       <c r="G72" s="1"/>
       <c r="J72" s="1"/>
     </row>
-    <row r="87" spans="3:4" x14ac:dyDescent="0.1">
+    <row r="87" spans="3:4">
       <c r="D87" s="1"/>
     </row>
-    <row r="88" spans="3:4" x14ac:dyDescent="0.1">
+    <row r="88" spans="3:4">
       <c r="C88" s="33"/>
       <c r="D88" s="1"/>
     </row>
@@ -12550,6 +12563,7 @@
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B12:E12"/>
   </mergeCells>
+  <phoneticPr fontId="33"/>
   <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0800-000000000000}">
       <formula1>"準委任,派遣,受託"</formula1>
@@ -12566,27 +12580,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0b07c111-1e65-491d-bd4a-55c961ced579">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5da815af-2352-44bc-8b3d-42b05d9842e4" xsi:nil="true"/>
-    <_x5bfe__x8c61__x30e6__x30fc__x30b6__x30fc_ xmlns="0b07c111-1e65-491d-bd4a-55c961ced579" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101007B9596178327C945B317B807C499E818" ma:contentTypeVersion="19" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="15faa7b26735d8ea89b804fdbd71df2f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0b07c111-1e65-491d-bd4a-55c961ced579" xmlns:ns3="5da815af-2352-44bc-8b3d-42b05d9842e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c06a27b2ad3302fbc8d1e0e366827c14" ns2:_="" ns3:_="">
     <xsd:import namespace="0b07c111-1e65-491d-bd4a-55c961ced579"/>
@@ -12841,7 +12834,48 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0b07c111-1e65-491d-bd4a-55c961ced579">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5da815af-2352-44bc-8b3d-42b05d9842e4" xsi:nil="true"/>
+    <_x5bfe__x8c61__x30e6__x30fc__x30b6__x30fc_ xmlns="0b07c111-1e65-491d-bd4a-55c961ced579" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71415BB7-EC5A-432A-B770-72D05EAF01FD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="0b07c111-1e65-491d-bd4a-55c961ced579"/>
+    <ds:schemaRef ds:uri="5da815af-2352-44bc-8b3d-42b05d9842e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8F25B2A-62FB-4F52-849B-AB5E0D7193DE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -12849,7 +12883,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{688C63C6-7071-4968-AB69-F93AB9E1A0B3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -12860,17 +12894,4 @@
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71415BB7-EC5A-432A-B770-72D05EAF01FD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="0b07c111-1e65-491d-bd4a-55c961ced579"/>
-    <ds:schemaRef ds:uri="5da815af-2352-44bc-8b3d-42b05d9842e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>